--- a/data/trending_integrated_20260910_11.xlsx
+++ b/data/trending_integrated_20260910_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5050</v>
+        <v>4965</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+152.50%</t>
+          <t>+148.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="F2" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G2" t="n">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>531594610533</v>
+        <v>549027106136</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 대상 업종 신재생에너지 관련 스펙주. 단기 급등 후 폭락 가능성 경고.</t>
+          <t>스팩주 특성상 단기 급등 및 급락 가능성 언급. 합병 대상 업종(신재생에너지) 관련 기대와 함께 투자 주의 당부.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '신재생에너지']</t>
+          <t>['스팩주', '급등', '급락']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H3" t="n">
         <v>0.07000000000000001</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15270</v>
+        <v>15190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+26.30%</t>
+          <t>+25.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="F4" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G4" t="n">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="H4" t="n">
         <v>0.03</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>247921657020</v>
+        <v>253549015365</v>
       </c>
       <c r="P4" t="n">
         <v>36200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유가 급등 및 지정학적 긴장 고조 속에서 상승 기대감 표출. 일부 투자자 매수세 유입 및 목표가 상향 의견.</t>
+          <t>트럼프의 유가 상승 용인, 이란 관련 긴장 고조 등 호재에 따른 급등 기대감 표출. 100달러 돌파 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '호르무즈', '매집']</t>
+          <t>['유가', '트럼프', '호재']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28350</v>
+        <v>28750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+22.20%</t>
+          <t>+23.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G5" t="n">
         <v>57</v>
-      </c>
-      <c r="F5" t="n">
-        <v>37</v>
-      </c>
-      <c r="G5" t="n">
-        <v>58</v>
       </c>
       <c r="H5" t="n">
         <v>7.54</v>
@@ -886,7 +886,7 @@
         <v>7.58</v>
       </c>
       <c r="O5" t="n">
-        <v>34292702950</v>
+        <v>35105886850</v>
       </c>
       <c r="P5" t="n">
         <v>34750</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13760</v>
+        <v>13700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.13%</t>
+          <t>+18.61%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
         <v>4.37</v>
@@ -978,7 +978,7 @@
         <v>4.63</v>
       </c>
       <c r="O6" t="n">
-        <v>82803467835</v>
+        <v>85268414640</v>
       </c>
       <c r="P6" t="n">
         <v>33575</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3582</v>
+        <v>3595</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+15.36%</t>
+          <t>+15.78%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,7 +1041,7 @@
         <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
         <v>39</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>19041100393</v>
+        <v>19721615468</v>
       </c>
       <c r="P7" t="n">
         <v>20800</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+15.06%</t>
+          <t>+14.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H8" t="n">
         <v>2.12</v>
@@ -1162,7 +1162,7 @@
         <v>2.07</v>
       </c>
       <c r="O8" t="n">
-        <v>155955208610</v>
+        <v>163247784052</v>
       </c>
       <c r="P8" t="n">
         <v>4795</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외국인 순매수와 상승 기대감 속 단기 급등 가능성 언급.</t>
+          <t>외인 매수세에도 불구하고 개인 매도 물량 출현, 단기적 등락 및 횡보 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인', '단타']</t>
+          <t>['외인', '개인', '횡보']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8350</v>
+        <v>8420</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+12.53%</t>
+          <t>+13.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>1006</v>
+        <v>1035</v>
       </c>
       <c r="H9" t="n">
         <v>1.17</v>
@@ -1254,7 +1254,7 @@
         <v>0.77</v>
       </c>
       <c r="O9" t="n">
-        <v>55674653350</v>
+        <v>58534622485</v>
       </c>
       <c r="P9" t="n">
         <v>21500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>폐암학회 참여 및 글로벌 제약사 협력, 항암제 내성 극복 기술 관련 기대감.</t>
+          <t>세계 최초 항암제 내성 극복 기술, 글로벌 제약사 임상 참여 등 강력한 호재 언급. FDA 임상 2상 승인 및 기술 이전 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['폐암학회', '항암제', 'FDA']</t>
+          <t>['항암제', '임상', 'FDA']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>535</v>
+        <v>3905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.31%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.38</v>
+        <v>-1.62</v>
       </c>
       <c r="E10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F10" t="n">
         <v>46</v>
       </c>
-      <c r="F10" t="n">
-        <v>25</v>
-      </c>
       <c r="G10" t="n">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>3810</v>
       </c>
       <c r="K10" t="n">
-        <v>510</v>
+        <v>3870</v>
       </c>
       <c r="L10" t="n">
-        <v>585</v>
+        <v>4250</v>
       </c>
       <c r="M10" t="n">
-        <v>504</v>
+        <v>3660</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>3.19</v>
       </c>
       <c r="O10" t="n">
-        <v>6543322512</v>
+        <v>121288248349</v>
       </c>
       <c r="P10" t="n">
-        <v>2610</v>
+        <v>8100</v>
       </c>
       <c r="Q10" t="n">
-        <v>255</v>
+        <v>592</v>
       </c>
       <c r="R10" t="n">
-        <v>-205000</v>
+        <v>20000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['투경', '6G', '장기전']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
         <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="H11" t="n">
         <v>0.85</v>
@@ -1438,7 +1438,7 @@
         <v>0.51</v>
       </c>
       <c r="O11" t="n">
-        <v>17027527097</v>
+        <v>17168553714</v>
       </c>
       <c r="P11" t="n">
         <v>2930</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>새만금 및 LH 관련 호재 언급, 지속 매수세 유입 및 저점 매수 권유.</t>
+          <t>새만금 사업 관련 긍정적 기대와 함께 지속적인 매수세 및 기관/외인 동향 분석. 저점 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['새만금', 'LH', '매수']</t>
+          <t>['새만금', '매수', '저점']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3890</v>
+        <v>517</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.10%</t>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.62</v>
+        <v>0.38</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="H12" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3810</v>
+        <v>508</v>
       </c>
       <c r="K12" t="n">
-        <v>3870</v>
+        <v>510</v>
       </c>
       <c r="L12" t="n">
-        <v>4250</v>
+        <v>585</v>
       </c>
       <c r="M12" t="n">
-        <v>3660</v>
+        <v>504</v>
       </c>
       <c r="N12" t="n">
-        <v>3.19</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>116605176718</v>
+        <v>6809773068</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>2610</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>255</v>
       </c>
       <c r="R12" t="n">
-        <v>20000</v>
+        <v>-205000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['투경', '6G', '장기전']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>152700</v>
+        <v>152500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="F13" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G13" t="n">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="H13" t="n">
         <v>15.65</v>
@@ -1616,13 +1616,13 @@
         <v>164700</v>
       </c>
       <c r="M13" t="n">
-        <v>152500</v>
+        <v>151200</v>
       </c>
       <c r="N13" t="n">
         <v>15.25</v>
       </c>
       <c r="O13" t="n">
-        <v>286363418450</v>
+        <v>298541756800</v>
       </c>
       <c r="P13" t="n">
         <v>164700</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유가 급등 및 정제마진 호조에 따른 주가 상승 기대감. JP모건 매수 패턴 분석.</t>
+          <t>유가 폭등, 정제마진 고공행진 등 긍정적 요인과 JP모건 대량매수 패턴 언급. 단기 상승 후 하락 가능성 시사.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', 'JP모건']</t>
+          <t>['유가', '정제마진', '매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1839000</v>
+        <v>1841000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="F14" t="n">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="G14" t="n">
-        <v>1449</v>
+        <v>1498</v>
       </c>
       <c r="H14" t="n">
         <v>50.67</v>
@@ -1714,7 +1714,7 @@
         <v>50.66</v>
       </c>
       <c r="O14" t="n">
-        <v>2573491113500</v>
+        <v>2684629860000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>ADR 상승에도 불구하고 외국인 매도세 및 시장 하락 우려, 반도체 업황 불확실성 언급.</t>
+          <t>SK하이닉스 주가 하락 및 부진에 대한 우려 표출. 옵션만기, 기관 매도 폭탄 등 부정적 요인 언급. 반등 가능성도 일부 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['ADR', '매도', '반도체']</t>
+          <t>['주가하락', '기관매도', '반등']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>265500</v>
+        <v>265000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="F15" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G15" t="n">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="H15" t="n">
         <v>46.81</v>
@@ -1806,7 +1806,7 @@
         <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1471260839250</v>
+        <v>1538151773250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락 및 약세 전망, 외인 매도 및 리스크 요인 언급.</t>
+          <t>삼성전자 주가 하락 및 부진에 대한 부정적 의견 다수. 자사주 매입, 매도 압력, 시장 전체 하락 등 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['매도', '리스크']</t>
+          <t>['주가하락', '매도', '시장']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14000</v>
+        <v>14030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.45</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H16" t="n">
         <v>6.09</v>
@@ -1898,7 +1898,7 @@
         <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>83811333770</v>
+        <v>86596103370</v>
       </c>
       <c r="P16" t="n">
         <v>30200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 관련 호재 언급. 주포의 움직임 및 공매도 금지에 대한 기대감.</t>
+          <t>미국 신규 원전 건설 관련 긍정적 전망과 공매도 금지 지정 효과 언급. 단기 상승 및 하락 가능성 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '주포']</t>
+          <t>['원전', '공매도', '상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18810</v>
+        <v>18790</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
         <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>57359692645</v>
+        <v>59269376720</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2035,79 +2035,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88500</v>
+        <v>14410</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.04</v>
+        <v>1.34</v>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="F18" t="n">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
-        <v>704</v>
+        <v>383</v>
       </c>
       <c r="H18" t="n">
-        <v>23.65</v>
+        <v>2.89</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>91700</v>
+        <v>14960</v>
       </c>
       <c r="K18" t="n">
-        <v>90000</v>
+        <v>15040</v>
       </c>
       <c r="L18" t="n">
-        <v>90700</v>
+        <v>15040</v>
       </c>
       <c r="M18" t="n">
-        <v>87800</v>
+        <v>14190</v>
       </c>
       <c r="N18" t="n">
-        <v>23.61</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>111294025550</v>
+        <v>71705179140</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>1263</v>
       </c>
       <c r="R18" t="n">
-        <v>-73000</v>
+        <v>-282000</v>
       </c>
       <c r="S18" t="n">
-        <v>-24000</v>
+        <v>-7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
+          <t>미국 광통신 관련주 강세, AI 관련주와 비교 언급. 외인 매수세 유입에 따른 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '웨스턴하우스', '호재']</t>
+          <t>['광통신', 'AI', '외인']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,86 +2120,86 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14410</v>
+        <v>88300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.34</v>
+        <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="G19" t="n">
-        <v>355</v>
+        <v>711</v>
       </c>
       <c r="H19" t="n">
-        <v>2.89</v>
+        <v>23.65</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14960</v>
+        <v>91700</v>
       </c>
       <c r="K19" t="n">
-        <v>15040</v>
+        <v>90000</v>
       </c>
       <c r="L19" t="n">
-        <v>15040</v>
+        <v>90700</v>
       </c>
       <c r="M19" t="n">
-        <v>14190</v>
+        <v>87800</v>
       </c>
       <c r="N19" t="n">
-        <v>1.55</v>
+        <v>23.61</v>
       </c>
       <c r="O19" t="n">
-        <v>70605598770</v>
+        <v>113882820350</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>1263</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-282000</v>
+        <v>-73000</v>
       </c>
       <c r="S19" t="n">
-        <v>-7000</v>
+        <v>-24000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 강세 및 AI 관련주 언급. 외인 매수세 유입과 함께 상승 추세 전망.</t>
+          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인']</t>
+          <t>['원전', '웨스턴하우스', '호재']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6540</v>
+        <v>14920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.66%</t>
+          <t>-4.60%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>225</v>
+        <v>283</v>
       </c>
       <c r="H20" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K20" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L20" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M20" t="n">
-        <v>6400</v>
+        <v>14700</v>
       </c>
       <c r="N20" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>8624612970</v>
+        <v>18715379445</v>
       </c>
       <c r="P20" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>-131000</v>
+        <v>-14000</v>
       </c>
       <c r="S20" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외인 매도세 및 주가 패턴에 대한 불만 제기. 자사주 소각 및 분사 이슈 언급.</t>
+          <t>건설업 흑자 전환 및 반도체 설계 용역 발주 소식에도 불구하고 하락세 지속. 투매 및 개별 종목 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['외인', '자사주', '분사']</t>
+          <t>['건설', '반도체', '투매']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,130 +2304,130 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12400</v>
+        <v>2150</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.83%</t>
+          <t>-4.87%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="H21" t="n">
-        <v>0.14</v>
+        <v>4.91</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13030</v>
+        <v>2260</v>
       </c>
       <c r="K21" t="n">
-        <v>13160</v>
+        <v>2250</v>
       </c>
       <c r="L21" t="n">
-        <v>13240</v>
+        <v>2290</v>
       </c>
       <c r="M21" t="n">
-        <v>12150</v>
+        <v>2080</v>
       </c>
       <c r="N21" t="n">
-        <v>0.36</v>
+        <v>5.26</v>
       </c>
       <c r="O21" t="n">
-        <v>53594021190</v>
+        <v>5233341095</v>
       </c>
       <c r="P21" t="n">
-        <v>20850</v>
+        <v>2705</v>
       </c>
       <c r="Q21" t="n">
-        <v>4020</v>
+        <v>1418</v>
       </c>
       <c r="R21" t="n">
-        <v>231000</v>
+        <v>-47000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
+          <t>적대적 M&amp;A 가능성 속 최대주주 변경. 5% 이상 하락하며 변동성 확대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['호재', '원전', '하락']</t>
+          <t>['M&amp;A', '최대주주', '변동성']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14880</v>
+        <v>6520</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>-4.96%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>15640</v>
+        <v>6860</v>
       </c>
       <c r="K22" t="n">
-        <v>15600</v>
+        <v>6800</v>
       </c>
       <c r="L22" t="n">
-        <v>15600</v>
+        <v>6820</v>
       </c>
       <c r="M22" t="n">
-        <v>14700</v>
+        <v>6400</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>16.71</v>
       </c>
       <c r="O22" t="n">
-        <v>18305161225</v>
+        <v>8728235050</v>
       </c>
       <c r="P22" t="n">
-        <v>19380</v>
+        <v>13000</v>
       </c>
       <c r="Q22" t="n">
-        <v>3200</v>
+        <v>6030</v>
       </c>
       <c r="R22" t="n">
-        <v>-14000</v>
+        <v>-131000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>건설업 흑자 전환 및 반도체 설계 용역 발주 소식에도 불구하고 하락세 지속. 투매 및 개별 종목 언급.</t>
+          <t>외인 매도세 및 주가 패턴에 대한 불만 제기. 자사주 소각 및 분사 이슈 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['건설', '반도체', '투매']</t>
+          <t>['외인', '자사주', '분사']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2140</v>
+        <v>12340</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.30%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>-0.22</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>0.14</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2260</v>
+        <v>13030</v>
       </c>
       <c r="K23" t="n">
-        <v>2250</v>
+        <v>13160</v>
       </c>
       <c r="L23" t="n">
-        <v>2290</v>
+        <v>13240</v>
       </c>
       <c r="M23" t="n">
-        <v>2080</v>
+        <v>12150</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>0.36</v>
       </c>
       <c r="O23" t="n">
-        <v>4488863295</v>
+        <v>54225418870</v>
       </c>
       <c r="P23" t="n">
-        <v>2705</v>
+        <v>20850</v>
       </c>
       <c r="Q23" t="n">
-        <v>1418</v>
+        <v>4020</v>
       </c>
       <c r="R23" t="n">
-        <v>-47000</v>
+        <v>231000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>적대적 M&amp;A 가능성 속 최대주주 변경. 5% 이상 하락하며 변동성 확대.</t>
+          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '최대주주', '변동성']</t>
+          <t>['호재', '원전', '하락']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,77 +2580,77 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3625</v>
+        <v>29050</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-6.59%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.54</v>
+        <v>0.17</v>
       </c>
       <c r="E24" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>12.31</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3865</v>
+        <v>31100</v>
       </c>
       <c r="K24" t="n">
-        <v>3845</v>
+        <v>30450</v>
       </c>
       <c r="L24" t="n">
-        <v>4075</v>
+        <v>30600</v>
       </c>
       <c r="M24" t="n">
-        <v>3605</v>
+        <v>28800</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>12.14</v>
       </c>
       <c r="O24" t="n">
-        <v>42234134029</v>
+        <v>45021105950</v>
       </c>
       <c r="P24" t="n">
-        <v>4335</v>
+        <v>75900</v>
       </c>
       <c r="Q24" t="n">
-        <v>1246</v>
+        <v>15000</v>
       </c>
       <c r="R24" t="n">
-        <v>-73000</v>
+        <v>-198000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,77 +2672,77 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29100</v>
+        <v>3605</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.43%</t>
+          <t>-6.73%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.17</v>
+        <v>-0.54</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="H25" t="n">
-        <v>12.31</v>
+        <v>1.54</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>31100</v>
+        <v>3865</v>
       </c>
       <c r="K25" t="n">
-        <v>30450</v>
+        <v>3845</v>
       </c>
       <c r="L25" t="n">
-        <v>30600</v>
+        <v>4075</v>
       </c>
       <c r="M25" t="n">
-        <v>28800</v>
+        <v>3605</v>
       </c>
       <c r="N25" t="n">
-        <v>12.14</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
-        <v>43759441025</v>
+        <v>43160955783</v>
       </c>
       <c r="P25" t="n">
-        <v>75900</v>
+        <v>4335</v>
       </c>
       <c r="Q25" t="n">
-        <v>15000</v>
+        <v>1246</v>
       </c>
       <c r="R25" t="n">
-        <v>-198000</v>
+        <v>-73000</v>
       </c>
       <c r="S25" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27850</v>
+        <v>28050</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.09%</t>
+          <t>-7.43%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.02</v>
       </c>
       <c r="E26" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F26" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G26" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>101204910175</v>
+        <v>103440821725</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>계단식 하락 및 주포 이탈 가능성 언급, 신규주 약세 전망.</t>
+          <t>계단식 하락 추세와 주포 이탈 가능성 언급. 투자 주의 및 매도 권유. 단기 상승 기대감도 존재.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['계단식 하락', '주포']</t>
+          <t>['계단식 하락', '주포 이탈', '매도 권유']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>-0.32</v>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F27" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>

--- a/data/trending_integrated_20260910_11.xlsx
+++ b/data/trending_integrated_20260910_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4965</v>
+        <v>4910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+148.25%</t>
+          <t>+145.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="F2" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G2" t="n">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>549027106136</v>
+        <v>557839665629</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -619,14 +619,14 @@
         <v>4000</v>
       </c>
       <c r="R2" t="n">
-        <v>-152000</v>
+        <v>-149000</v>
       </c>
       <c r="S2" t="n">
-        <v>-2278000</v>
+        <v>-2304000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스팩주 특성상 단기 급등 및 급락 가능성 언급. 합병 대상 업종(신재생에너지) 관련 기대와 함께 투자 주의 당부.</t>
+          <t>신재생에너지 합병 대상 스팩주로 단기 급등 가능성 있으나, 과도한 기대는 경계해야 함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '급등', '급락']</t>
+          <t>['스팩주', '합병', '기대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -676,7 +676,7 @@
         <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" t="n">
         <v>0.07000000000000001</v>
@@ -711,7 +711,7 @@
         <v>133</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -747,184 +747,184 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15190</v>
+        <v>29050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+25.64%</t>
+          <t>+25.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>310</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>350</v>
+        <v>62</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03</v>
+        <v>7.54</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12090</v>
+        <v>23200</v>
       </c>
       <c r="K4" t="n">
-        <v>12730</v>
+        <v>26900</v>
       </c>
       <c r="L4" t="n">
-        <v>15710</v>
+        <v>30150</v>
       </c>
       <c r="M4" t="n">
-        <v>12720</v>
+        <v>24500</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>253549015365</v>
+        <v>36128612300</v>
       </c>
       <c r="P4" t="n">
-        <v>36200</v>
+        <v>34750</v>
       </c>
       <c r="Q4" t="n">
-        <v>8920</v>
+        <v>20450</v>
       </c>
       <c r="R4" t="n">
-        <v>39000</v>
+        <v>-47000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>트럼프의 유가 상승 용인, 이란 관련 긴장 고조 등 호재에 따른 급등 기대감 표출. 100달러 돌파 언급.</t>
+          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '트럼프', '호재']</t>
+          <t>['자사주', '소각', '주주환원']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28750</v>
+        <v>15080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+23.92%</t>
+          <t>+24.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>319</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>196</v>
       </c>
       <c r="G5" t="n">
-        <v>57</v>
+        <v>368</v>
       </c>
       <c r="H5" t="n">
-        <v>7.54</v>
+        <v>0.03</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23200</v>
+        <v>12090</v>
       </c>
       <c r="K5" t="n">
-        <v>26900</v>
+        <v>12730</v>
       </c>
       <c r="L5" t="n">
-        <v>30150</v>
+        <v>15710</v>
       </c>
       <c r="M5" t="n">
-        <v>24500</v>
+        <v>12720</v>
       </c>
       <c r="N5" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>35105886850</v>
+        <v>258511695145</v>
       </c>
       <c r="P5" t="n">
-        <v>34750</v>
+        <v>36200</v>
       </c>
       <c r="Q5" t="n">
-        <v>20450</v>
+        <v>8920</v>
       </c>
       <c r="R5" t="n">
-        <v>-37000</v>
+        <v>22000</v>
       </c>
       <c r="S5" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
+          <t>지정학적 리스크 고조 및 유가 급등으로 인한 강한 상승세. 상한가 마감 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주', '소각', '주주환원']</t>
+          <t>['유가', '급등', '상한가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13700</v>
+        <v>13470</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+18.61%</t>
+          <t>+16.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
         <v>4.37</v>
@@ -978,7 +978,7 @@
         <v>4.63</v>
       </c>
       <c r="O6" t="n">
-        <v>85268414640</v>
+        <v>86776544745</v>
       </c>
       <c r="P6" t="n">
         <v>33575</v>
@@ -987,7 +987,7 @@
         <v>9690</v>
       </c>
       <c r="R6" t="n">
-        <v>12000</v>
+        <v>-78000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3595</v>
+        <v>3555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+15.78%</t>
+          <t>+14.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>19721615468</v>
+        <v>19944669143</v>
       </c>
       <c r="P7" t="n">
         <v>20800</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2015</v>
+        <v>1997</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+14.49%</t>
+          <t>+13.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="H8" t="n">
         <v>2.12</v>
@@ -1162,7 +1162,7 @@
         <v>2.07</v>
       </c>
       <c r="O8" t="n">
-        <v>163247784052</v>
+        <v>166150108824</v>
       </c>
       <c r="P8" t="n">
         <v>4795</v>
@@ -1171,14 +1171,14 @@
         <v>1524</v>
       </c>
       <c r="R8" t="n">
-        <v>283000</v>
+        <v>-706000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 매수세에도 불구하고 개인 매도 물량 출현, 단기적 등락 및 횡보 가능성 언급.</t>
+          <t>외국인 매수세 유입에도 불구하고 관망세 짙음. 단기 시세 분출 기대감 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인', '개인', '횡보']</t>
+          <t>['외인', '시세', '기대']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8420</v>
+        <v>8330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+13.48%</t>
+          <t>+12.26%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G9" t="n">
-        <v>1035</v>
+        <v>1070</v>
       </c>
       <c r="H9" t="n">
         <v>1.17</v>
@@ -1254,7 +1254,7 @@
         <v>0.77</v>
       </c>
       <c r="O9" t="n">
-        <v>58534622485</v>
+        <v>59433620675</v>
       </c>
       <c r="P9" t="n">
         <v>21500</v>
@@ -1263,23 +1263,23 @@
         <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>100000</v>
+        <v>117000</v>
       </c>
       <c r="S9" t="n">
         <v>-8000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>세계 최초 항암제 내성 극복 기술, 글로벌 제약사 임상 참여 등 강력한 호재 언급. FDA 임상 2상 승인 및 기술 이전 기대.</t>
+          <t>세계 최초 항암제 내성 극복 관련 글로벌 학회 참여 및 기술 이전 가능성. 4연상 이상 기대감 고조.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['항암제', '임상', 'FDA']</t>
+          <t>['항암제', '내성 극복', '기술 이전']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3905</v>
+        <v>2170</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>+4.08%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.62</v>
+        <v>0.34</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="H10" t="n">
-        <v>1.57</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3810</v>
+        <v>2085</v>
       </c>
       <c r="K10" t="n">
-        <v>3870</v>
+        <v>2255</v>
       </c>
       <c r="L10" t="n">
-        <v>4250</v>
+        <v>2395</v>
       </c>
       <c r="M10" t="n">
-        <v>3660</v>
+        <v>2040</v>
       </c>
       <c r="N10" t="n">
-        <v>3.19</v>
+        <v>0.51</v>
       </c>
       <c r="O10" t="n">
-        <v>121288248349</v>
+        <v>17378690650</v>
       </c>
       <c r="P10" t="n">
-        <v>8100</v>
+        <v>2930</v>
       </c>
       <c r="Q10" t="n">
-        <v>592</v>
+        <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>20000</v>
+        <v>-175000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
+          <t>새만금 사업 및 LH 관련 계약 추정. 외국인 및 기타 법인의 지속적인 매수세 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['투경', '6G', '장기전']</t>
+          <t>['새만금', 'LH', '매수세']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,43 +1379,43 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2130</v>
+        <v>3900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>-1.62</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
         <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="H11" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2085</v>
+        <v>3810</v>
       </c>
       <c r="K11" t="n">
-        <v>2255</v>
+        <v>3870</v>
       </c>
       <c r="L11" t="n">
-        <v>2395</v>
+        <v>4250</v>
       </c>
       <c r="M11" t="n">
-        <v>2040</v>
+        <v>3660</v>
       </c>
       <c r="N11" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="O11" t="n">
-        <v>17168553714</v>
+        <v>122608631458</v>
       </c>
       <c r="P11" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-4000</v>
+        <v>-540000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>새만금 사업 관련 긍정적 기대와 함께 지속적인 매수세 및 기관/외인 동향 분석. 저점 매수 기회 언급.</t>
+          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['새만금', '매수', '저점']</t>
+          <t>['투경', '6G', '장기전']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.38</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H12" t="n">
         <v>2.8</v>
@@ -1530,7 +1530,7 @@
         <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>6809773068</v>
+        <v>7065120312</v>
       </c>
       <c r="P12" t="n">
         <v>2610</v>
@@ -1539,7 +1539,7 @@
         <v>255</v>
       </c>
       <c r="R12" t="n">
-        <v>-205000</v>
+        <v>-263000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>152500</v>
+        <v>1846000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>322</v>
+        <v>797</v>
       </c>
       <c r="F13" t="n">
-        <v>154</v>
+        <v>457</v>
       </c>
       <c r="G13" t="n">
-        <v>790</v>
+        <v>1555</v>
       </c>
       <c r="H13" t="n">
-        <v>15.65</v>
+        <v>50.67</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>153500</v>
+        <v>1856000</v>
       </c>
       <c r="K13" t="n">
-        <v>155500</v>
+        <v>1879000</v>
       </c>
       <c r="L13" t="n">
-        <v>164700</v>
+        <v>1890000</v>
       </c>
       <c r="M13" t="n">
-        <v>151200</v>
+        <v>1811000</v>
       </c>
       <c r="N13" t="n">
-        <v>15.25</v>
+        <v>50.66</v>
       </c>
       <c r="O13" t="n">
-        <v>298541756800</v>
+        <v>2786062796500</v>
       </c>
       <c r="P13" t="n">
-        <v>164700</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>87700</v>
+        <v>293000</v>
       </c>
       <c r="R13" t="n">
-        <v>112000</v>
+        <v>-110000</v>
       </c>
       <c r="S13" t="n">
-        <v>-5000</v>
+        <v>-78000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유가 폭등, 정제마진 고공행진 등 긍정적 요인과 JP모건 대량매수 패턴 언급. 단기 상승 후 하락 가능성 시사.</t>
+          <t>자사주 소각 및 ADR 상승에도 불구하고, 개인 투자자들의 매도 압력 및 하락 우려 존재. 단기 변동성 확대 예상.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', '매수']</t>
+          <t>['자사주', '매도', '변동성']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1841000</v>
+        <v>152400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>792</v>
+        <v>329</v>
       </c>
       <c r="F14" t="n">
-        <v>461</v>
+        <v>156</v>
       </c>
       <c r="G14" t="n">
-        <v>1498</v>
+        <v>800</v>
       </c>
       <c r="H14" t="n">
-        <v>50.67</v>
+        <v>15.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1856000</v>
+        <v>153500</v>
       </c>
       <c r="K14" t="n">
-        <v>1879000</v>
+        <v>155500</v>
       </c>
       <c r="L14" t="n">
-        <v>1890000</v>
+        <v>164700</v>
       </c>
       <c r="M14" t="n">
-        <v>1811000</v>
+        <v>151200</v>
       </c>
       <c r="N14" t="n">
-        <v>50.66</v>
+        <v>15.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2684629860000</v>
+        <v>302233049850</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q14" t="n">
-        <v>293000</v>
+        <v>87700</v>
       </c>
       <c r="R14" t="n">
-        <v>-64000</v>
+        <v>104000</v>
       </c>
       <c r="S14" t="n">
-        <v>-67000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 하락 및 부진에 대한 우려 표출. 옵션만기, 기관 매도 폭탄 등 부정적 요인 언급. 반등 가능성도 일부 존재.</t>
+          <t>유가 상승으로 인한 단기 호재 기대감 있으나, 원유 관련 주가 상승 지속성에 대한 의구심 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가하락', '기관매도', '반등']</t>
+          <t>['유가', '호재', '의구심']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>265000</v>
+        <v>266000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="F15" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G15" t="n">
-        <v>1269</v>
+        <v>1289</v>
       </c>
       <c r="H15" t="n">
         <v>46.81</v>
@@ -1806,7 +1806,7 @@
         <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1538151773250</v>
+        <v>1608502070000</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,23 +1815,23 @@
         <v>71600</v>
       </c>
       <c r="R15" t="n">
-        <v>236000</v>
+        <v>376000</v>
       </c>
       <c r="S15" t="n">
-        <v>-272000</v>
+        <v>-400000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성전자 주가 하락 및 부진에 대한 부정적 의견 다수. 자사주 매입, 매도 압력, 시장 전체 하락 등 언급.</t>
+          <t>타 종목 대비 부진한 흐름 및 개인 투자자들의 매도 심리 고조. 급락 가능성 경고.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가하락', '매도', '시장']</t>
+          <t>['매도', '부진', '급락']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14030</v>
+        <v>14080</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.45</v>
       </c>
       <c r="E16" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="H16" t="n">
         <v>6.09</v>
@@ -1898,7 +1898,7 @@
         <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>86596103370</v>
+        <v>89218777760</v>
       </c>
       <c r="P16" t="n">
         <v>30200</v>
@@ -1907,23 +1907,23 @@
         <v>3540</v>
       </c>
       <c r="R16" t="n">
-        <v>-70000</v>
+        <v>-132000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 관련 긍정적 전망과 공매도 금지 지정 효과 언급. 단기 상승 및 하락 가능성 혼재.</t>
+          <t>미국 신규 원전 건설 및 공매도 금지 이슈 부각. 단기 급등 가능성 및 양전 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '상승']</t>
+          <t>['원전', '공매도 금지', '양전']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18790</v>
+        <v>19000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>59269376720</v>
+        <v>62506504830</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -1999,10 +1999,10 @@
         <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>58000</v>
+        <v>-67000</v>
       </c>
       <c r="S17" t="n">
-        <v>-29000</v>
+        <v>-52000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2035,79 +2035,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14410</v>
+        <v>88800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.34</v>
+        <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="G18" t="n">
-        <v>383</v>
+        <v>720</v>
       </c>
       <c r="H18" t="n">
-        <v>2.89</v>
+        <v>23.65</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14960</v>
+        <v>91700</v>
       </c>
       <c r="K18" t="n">
-        <v>15040</v>
+        <v>90000</v>
       </c>
       <c r="L18" t="n">
-        <v>15040</v>
+        <v>90700</v>
       </c>
       <c r="M18" t="n">
-        <v>14190</v>
+        <v>87800</v>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>23.61</v>
       </c>
       <c r="O18" t="n">
-        <v>71705179140</v>
+        <v>117062817600</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>1263</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-282000</v>
+        <v>-273000</v>
       </c>
       <c r="S18" t="n">
-        <v>-7000</v>
+        <v>31000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 강세, AI 관련주와 비교 언급. 외인 매수세 유입에 따른 상승 기대감 표출.</t>
+          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인']</t>
+          <t>['원전', '웨스턴하우스', '호재']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,86 +2120,86 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88300</v>
+        <v>14420</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.04</v>
+        <v>1.34</v>
       </c>
       <c r="E19" t="n">
-        <v>195</v>
+        <v>119</v>
       </c>
       <c r="F19" t="n">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>711</v>
+        <v>394</v>
       </c>
       <c r="H19" t="n">
-        <v>23.65</v>
+        <v>2.89</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>91700</v>
+        <v>14960</v>
       </c>
       <c r="K19" t="n">
-        <v>90000</v>
+        <v>15040</v>
       </c>
       <c r="L19" t="n">
-        <v>90700</v>
+        <v>15040</v>
       </c>
       <c r="M19" t="n">
-        <v>87800</v>
+        <v>14190</v>
       </c>
       <c r="N19" t="n">
-        <v>23.61</v>
+        <v>1.55</v>
       </c>
       <c r="O19" t="n">
-        <v>113882820350</v>
+        <v>72584121725</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>1263</v>
       </c>
       <c r="R19" t="n">
-        <v>-73000</v>
+        <v>-492000</v>
       </c>
       <c r="S19" t="n">
-        <v>-24000</v>
+        <v>-7000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
+          <t>미국 광통신 관련주로 분류되며, 외인 매수세 유입에 대한 기대감이 존재함. 다만, 뚜렷한 근거 제시 없이 주가 상승에 대한 희망적인 언급이 주를 이룸.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '웨스턴하우스', '호재']</t>
+          <t>['광통신', '외인', 'AI']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14920</v>
+        <v>15060</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.60%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>18715379445</v>
+        <v>19118462915</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2275,7 +2275,7 @@
         <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>-14000</v>
+        <v>1000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2150</v>
+        <v>6600</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.87%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.35</v>
+        <v>-1.03</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="H21" t="n">
-        <v>4.91</v>
+        <v>15.68</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2260</v>
+        <v>6860</v>
       </c>
       <c r="K21" t="n">
-        <v>2250</v>
+        <v>6800</v>
       </c>
       <c r="L21" t="n">
-        <v>2290</v>
+        <v>6820</v>
       </c>
       <c r="M21" t="n">
-        <v>2080</v>
+        <v>6400</v>
       </c>
       <c r="N21" t="n">
-        <v>5.26</v>
+        <v>16.71</v>
       </c>
       <c r="O21" t="n">
-        <v>5233341095</v>
+        <v>9037631490</v>
       </c>
       <c r="P21" t="n">
-        <v>2705</v>
+        <v>13000</v>
       </c>
       <c r="Q21" t="n">
-        <v>1418</v>
+        <v>6030</v>
       </c>
       <c r="R21" t="n">
-        <v>-47000</v>
+        <v>-273000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>적대적 M&amp;A 가능성 속 최대주주 변경. 5% 이상 하락하며 변동성 확대.</t>
+          <t>경영진 퇴출 요구 및 주가 조작 의혹 등 부정적인 여론이 지배적임. 실질적인 근거 제시 없이 불만과 의혹 제기가 대부분을 차지함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['M&amp;A', '최대주주', '변동성']</t>
+          <t>['주가조작', '외국인', '김동선']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,77 +2396,77 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6520</v>
+        <v>12330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.96%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.03</v>
+        <v>-0.22</v>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G22" t="n">
-        <v>231</v>
+        <v>65</v>
       </c>
       <c r="H22" t="n">
-        <v>15.68</v>
+        <v>0.14</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6860</v>
+        <v>13030</v>
       </c>
       <c r="K22" t="n">
-        <v>6800</v>
+        <v>13160</v>
       </c>
       <c r="L22" t="n">
-        <v>6820</v>
+        <v>13240</v>
       </c>
       <c r="M22" t="n">
-        <v>6400</v>
+        <v>12150</v>
       </c>
       <c r="N22" t="n">
-        <v>16.71</v>
+        <v>0.36</v>
       </c>
       <c r="O22" t="n">
-        <v>8728235050</v>
+        <v>54817417760</v>
       </c>
       <c r="P22" t="n">
-        <v>13000</v>
+        <v>20850</v>
       </c>
       <c r="Q22" t="n">
-        <v>6030</v>
+        <v>4020</v>
       </c>
       <c r="R22" t="n">
-        <v>-131000</v>
+        <v>25000</v>
       </c>
       <c r="S22" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>외인 매도세 및 주가 패턴에 대한 불만 제기. 자사주 소각 및 분사 이슈 언급.</t>
+          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['외인', '자사주', '분사']</t>
+          <t>['호재', '원전', '하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,169 +2488,169 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12340</v>
+        <v>2135</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.30%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="H23" t="n">
-        <v>0.14</v>
+        <v>4.91</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>13030</v>
+        <v>2260</v>
       </c>
       <c r="K23" t="n">
-        <v>13160</v>
+        <v>2250</v>
       </c>
       <c r="L23" t="n">
-        <v>13240</v>
+        <v>2290</v>
       </c>
       <c r="M23" t="n">
-        <v>12150</v>
+        <v>2080</v>
       </c>
       <c r="N23" t="n">
-        <v>0.36</v>
+        <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>54225418870</v>
+        <v>5531431540</v>
       </c>
       <c r="P23" t="n">
-        <v>20850</v>
+        <v>2705</v>
       </c>
       <c r="Q23" t="n">
-        <v>4020</v>
+        <v>1418</v>
       </c>
       <c r="R23" t="n">
-        <v>231000</v>
+        <v>-133000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
+          <t>M&amp;A 관련 이슈 및 새 최대주주 등장으로 인한 경영권 분쟁 가능성. 단기 급등락 예상.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['호재', '원전', '하락']</t>
+          <t>['M&amp;A', '경영권 분쟁', '최대주주']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29050</v>
+        <v>3640</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-6.59%</t>
+          <t>-5.82%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.17</v>
+        <v>-0.54</v>
       </c>
       <c r="E24" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H24" t="n">
-        <v>12.31</v>
+        <v>1.54</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>31100</v>
+        <v>3865</v>
       </c>
       <c r="K24" t="n">
-        <v>30450</v>
+        <v>3845</v>
       </c>
       <c r="L24" t="n">
-        <v>30600</v>
+        <v>4075</v>
       </c>
       <c r="M24" t="n">
-        <v>28800</v>
+        <v>3605</v>
       </c>
       <c r="N24" t="n">
-        <v>12.14</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
-        <v>45021105950</v>
+        <v>43517772876</v>
       </c>
       <c r="P24" t="n">
-        <v>75900</v>
+        <v>4335</v>
       </c>
       <c r="Q24" t="n">
-        <v>15000</v>
+        <v>1246</v>
       </c>
       <c r="R24" t="n">
-        <v>-198000</v>
+        <v>-210000</v>
       </c>
       <c r="S24" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,77 +2672,77 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3605</v>
+        <v>29250</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.73%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.54</v>
+        <v>0.17</v>
       </c>
       <c r="E25" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H25" t="n">
-        <v>1.54</v>
+        <v>12.31</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3865</v>
+        <v>31100</v>
       </c>
       <c r="K25" t="n">
-        <v>3845</v>
+        <v>30450</v>
       </c>
       <c r="L25" t="n">
-        <v>4075</v>
+        <v>30600</v>
       </c>
       <c r="M25" t="n">
-        <v>3605</v>
+        <v>28800</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>12.14</v>
       </c>
       <c r="O25" t="n">
-        <v>43160955783</v>
+        <v>45781362575</v>
       </c>
       <c r="P25" t="n">
-        <v>4335</v>
+        <v>75900</v>
       </c>
       <c r="Q25" t="n">
-        <v>1246</v>
+        <v>15000</v>
       </c>
       <c r="R25" t="n">
-        <v>-73000</v>
+        <v>-343000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2786,13 +2786,13 @@
         <v>0.02</v>
       </c>
       <c r="E26" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F26" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G26" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>103440821725</v>
+        <v>104898164475</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2827,23 +2827,23 @@
         <v>8200</v>
       </c>
       <c r="R26" t="n">
-        <v>-1000</v>
+        <v>12000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>계단식 하락 추세와 주포 이탈 가능성 언급. 투자 주의 및 매도 권유. 단기 상승 기대감도 존재.</t>
+          <t>수면무호흡증 관련 뉴스가 있으나, 계단식 하락 추세 및 저점 지속 하락에 대한 우려가 큼. 주포 이탈 및 투자자들의 부정적인 전망이 우세함.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['계단식 하락', '주포 이탈', '매도 권유']</t>
+          <t>['계단식 하락', '수면무호흡증', '주포']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>-0.32</v>
       </c>
       <c r="E27" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
         <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>
@@ -2919,7 +2919,7 @@
         <v>137</v>
       </c>
       <c r="R27" t="n">
-        <v>29000</v>
+        <v>25000</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260910_11.xlsx
+++ b/data/trending_integrated_20260910_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4910</v>
+        <v>4890</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+145.50%</t>
+          <t>+144.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G2" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>557839665629</v>
+        <v>565000242276</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신재생에너지 합병 대상 스팩주로 단기 급등 가능성 있으나, 과도한 기대는 경계해야 함.</t>
+          <t>합병 대상 업종 신재생에너지 관련 기대감. 스펙주 특성상 신중론.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '합병', '기대']</t>
+          <t>['스펙주', '신재생에너지', '합병']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H3" t="n">
         <v>0.07000000000000001</v>
@@ -702,7 +702,7 @@
         <v>0.08</v>
       </c>
       <c r="O3" t="n">
-        <v>472924463</v>
+        <v>551959243</v>
       </c>
       <c r="P3" t="n">
         <v>3660</v>
@@ -747,184 +747,184 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29050</v>
+        <v>15120</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+25.22%</t>
+          <t>+25.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="G4" t="n">
-        <v>62</v>
+        <v>371</v>
       </c>
       <c r="H4" t="n">
-        <v>7.54</v>
+        <v>0.03</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>23200</v>
+        <v>12090</v>
       </c>
       <c r="K4" t="n">
-        <v>26900</v>
+        <v>12730</v>
       </c>
       <c r="L4" t="n">
-        <v>30150</v>
+        <v>15710</v>
       </c>
       <c r="M4" t="n">
-        <v>24500</v>
+        <v>12720</v>
       </c>
       <c r="N4" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>36128612300</v>
+        <v>260338661495</v>
       </c>
       <c r="P4" t="n">
-        <v>34750</v>
+        <v>36200</v>
       </c>
       <c r="Q4" t="n">
-        <v>20450</v>
+        <v>8920</v>
       </c>
       <c r="R4" t="n">
-        <v>-47000</v>
+        <v>22000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
+          <t>이란발 긴장 고조 및 유가 급등에 따른 폭발적 상승 기대. 거래량 증가.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주', '소각', '주주환원']</t>
+          <t>['유가', '이란', '폭등']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15080</v>
+        <v>28850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+24.73%</t>
+          <t>+24.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>319</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>368</v>
+        <v>68</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>7.54</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12090</v>
+        <v>23200</v>
       </c>
       <c r="K5" t="n">
-        <v>12730</v>
+        <v>26900</v>
       </c>
       <c r="L5" t="n">
-        <v>15710</v>
+        <v>30150</v>
       </c>
       <c r="M5" t="n">
-        <v>12720</v>
+        <v>24500</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="O5" t="n">
-        <v>258511695145</v>
+        <v>36672708875</v>
       </c>
       <c r="P5" t="n">
-        <v>36200</v>
+        <v>34750</v>
       </c>
       <c r="Q5" t="n">
-        <v>8920</v>
+        <v>20450</v>
       </c>
       <c r="R5" t="n">
-        <v>22000</v>
+        <v>-47000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>지정학적 리스크 고조 및 유가 급등으로 인한 강한 상승세. 상한가 마감 기대감.</t>
+          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '급등', '상한가']</t>
+          <t>['자사주', '소각', '주주환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13470</v>
+        <v>13590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.62%</t>
+          <t>+17.66%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
         <v>4.37</v>
@@ -978,7 +978,7 @@
         <v>4.63</v>
       </c>
       <c r="O6" t="n">
-        <v>86776544745</v>
+        <v>87782617785</v>
       </c>
       <c r="P6" t="n">
         <v>33575</v>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3555</v>
+        <v>3600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+14.49%</t>
+          <t>+15.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
         <v>40</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>19944669143</v>
+        <v>20120036970</v>
       </c>
       <c r="P7" t="n">
         <v>20800</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+13.47%</t>
+          <t>+13.58%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H8" t="n">
         <v>2.12</v>
@@ -1162,7 +1162,7 @@
         <v>2.07</v>
       </c>
       <c r="O8" t="n">
-        <v>166150108824</v>
+        <v>168048152953</v>
       </c>
       <c r="P8" t="n">
         <v>4795</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입에도 불구하고 관망세 짙음. 단기 시세 분출 기대감 존재.</t>
+          <t>외인 매수세 속 단기 상승 기대감. 120일선 돌파 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인', '시세', '기대']</t>
+          <t>['120일선', '외인']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8330</v>
+        <v>8300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+12.26%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G9" t="n">
-        <v>1070</v>
+        <v>1111</v>
       </c>
       <c r="H9" t="n">
         <v>1.17</v>
@@ -1254,7 +1254,7 @@
         <v>0.77</v>
       </c>
       <c r="O9" t="n">
-        <v>59433620675</v>
+        <v>59984693265</v>
       </c>
       <c r="P9" t="n">
         <v>21500</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2170</v>
+        <v>525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.08%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>193</v>
+        <v>59</v>
       </c>
       <c r="H10" t="n">
-        <v>0.85</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2085</v>
+        <v>508</v>
       </c>
       <c r="K10" t="n">
-        <v>2255</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>2395</v>
+        <v>585</v>
       </c>
       <c r="M10" t="n">
-        <v>2040</v>
+        <v>504</v>
       </c>
       <c r="N10" t="n">
-        <v>0.51</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>17378690650</v>
+        <v>7397205472</v>
       </c>
       <c r="P10" t="n">
-        <v>2930</v>
+        <v>2610</v>
       </c>
       <c r="Q10" t="n">
-        <v>910</v>
+        <v>255</v>
       </c>
       <c r="R10" t="n">
-        <v>-175000</v>
+        <v>-263000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>새만금 사업 및 LH 관련 계약 추정. 외국인 및 기타 법인의 지속적인 매수세 확인.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['새만금', 'LH', '매수세']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3900</v>
+        <v>3895</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-1.62</v>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
         <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H11" t="n">
         <v>1.57</v>
@@ -1438,7 +1438,7 @@
         <v>3.19</v>
       </c>
       <c r="O11" t="n">
-        <v>122608631458</v>
+        <v>123782183524</v>
       </c>
       <c r="P11" t="n">
         <v>8100</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>510</v>
+        <v>2130</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>508</v>
+        <v>2085</v>
       </c>
       <c r="K12" t="n">
-        <v>510</v>
+        <v>2255</v>
       </c>
       <c r="L12" t="n">
-        <v>585</v>
+        <v>2395</v>
       </c>
       <c r="M12" t="n">
-        <v>504</v>
+        <v>2040</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>0.51</v>
       </c>
       <c r="O12" t="n">
-        <v>7065120312</v>
+        <v>17658449160</v>
       </c>
       <c r="P12" t="n">
-        <v>2610</v>
+        <v>2930</v>
       </c>
       <c r="Q12" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="R12" t="n">
-        <v>-263000</v>
+        <v>-175000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>새만금 사업 및 LH 관련 계약 추정. 외국인 및 기타 법인의 지속적인 매수세 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['새만금', 'LH', '매수세']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1846000</v>
+        <v>1850000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>797</v>
       </c>
       <c r="F13" t="n">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G13" t="n">
-        <v>1555</v>
+        <v>1628</v>
       </c>
       <c r="H13" t="n">
         <v>50.67</v>
@@ -1622,7 +1622,7 @@
         <v>50.66</v>
       </c>
       <c r="O13" t="n">
-        <v>2786062796500</v>
+        <v>2881254072000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자사주 소각 및 ADR 상승에도 불구하고, 개인 투자자들의 매도 압력 및 하락 우려 존재. 단기 변동성 확대 예상.</t>
+          <t>자사주 소각 및 ADR 상승에도 불구하고 매도 폭탄 및 패닉셀 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주', '매도', '변동성']</t>
+          <t>['자사주소각', 'ADR', '패닉셀']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>152400</v>
+        <v>152100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F14" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G14" t="n">
-        <v>800</v>
+        <v>836</v>
       </c>
       <c r="H14" t="n">
         <v>15.65</v>
@@ -1714,7 +1714,7 @@
         <v>15.25</v>
       </c>
       <c r="O14" t="n">
-        <v>302233049850</v>
+        <v>304937284400</v>
       </c>
       <c r="P14" t="n">
         <v>164700</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유가 상승으로 인한 단기 호재 기대감 있으나, 원유 관련 주가 상승 지속성에 대한 의구심 존재.</t>
+          <t>유가 폭등 수혜 기대감 속 개인 투자자 우려. JP모건 대량매수 패턴 분석.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가', '호재', '의구심']</t>
+          <t>['유가폭등', 'JP모건', '수익']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="F15" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G15" t="n">
-        <v>1289</v>
+        <v>1258</v>
       </c>
       <c r="H15" t="n">
         <v>46.81</v>
@@ -1806,7 +1806,7 @@
         <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1608502070000</v>
+        <v>1681300955750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>타 종목 대비 부진한 흐름 및 개인 투자자들의 매도 심리 고조. 급락 가능성 경고.</t>
+          <t>자사주 매입 리스크 및 매도 의견 다수. 코스피 폭락 및 급락 예상.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['매도', '부진', '급락']</t>
+          <t>['자사주매입', '매도', '폭락']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14080</v>
+        <v>14070</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.45</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="H16" t="n">
         <v>6.09</v>
@@ -1898,7 +1898,7 @@
         <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>89218777760</v>
+        <v>90891616800</v>
       </c>
       <c r="P16" t="n">
         <v>30200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 및 공매도 금지 이슈 부각. 단기 급등 가능성 및 양전 기대감.</t>
+          <t>미국 신규 원전 건설 소식 기반 상승 기대. 공매도 금지 관련 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '공매도 금지', '양전']</t>
+          <t>['원전', '공매도', '건설']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19000</v>
+        <v>18960</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>62506504830</v>
+        <v>63854324265</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88800</v>
+        <v>88900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F18" t="n">
         <v>133</v>
       </c>
       <c r="G18" t="n">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2082,7 +2082,7 @@
         <v>23.61</v>
       </c>
       <c r="O18" t="n">
-        <v>117062817600</v>
+        <v>120616112800</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14420</v>
+        <v>14400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.61%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="H19" t="n">
         <v>2.89</v>
@@ -2174,7 +2174,7 @@
         <v>1.55</v>
       </c>
       <c r="O19" t="n">
-        <v>72584121725</v>
+        <v>73352567185</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로 분류되며, 외인 매수세 유입에 대한 기대감이 존재함. 다만, 뚜렷한 근거 제시 없이 주가 상승에 대한 희망적인 언급이 주를 이룸.</t>
+          <t>미국 광통신주 강세 속 국내 동반 상승 기대. 외인 매수세 변화 관찰.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '외인', 'AI']</t>
+          <t>['광통신', 'AI', '외국인']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15060</v>
+        <v>6600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>293</v>
+        <v>241</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15640</v>
+        <v>6860</v>
       </c>
       <c r="K20" t="n">
-        <v>15600</v>
+        <v>6800</v>
       </c>
       <c r="L20" t="n">
-        <v>15600</v>
+        <v>6820</v>
       </c>
       <c r="M20" t="n">
-        <v>14700</v>
+        <v>6400</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>16.71</v>
       </c>
       <c r="O20" t="n">
-        <v>19118462915</v>
+        <v>9511142180</v>
       </c>
       <c r="P20" t="n">
-        <v>19380</v>
+        <v>13000</v>
       </c>
       <c r="Q20" t="n">
-        <v>3200</v>
+        <v>6030</v>
       </c>
       <c r="R20" t="n">
-        <v>1000</v>
+        <v>-273000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>건설업 흑자 전환 및 반도체 설계 용역 발주 소식에도 불구하고 하락세 지속. 투매 및 개별 종목 언급.</t>
+          <t>경영진 퇴출 요구 및 주가 조작 의혹 등 부정적인 여론이 지배적임. 실질적인 근거 제시 없이 불만과 의혹 제기가 대부분을 차지함.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,51 +2291,51 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['건설', '반도체', '투매']</t>
+          <t>['주가조작', '외국인', '김동선']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6600</v>
+        <v>14960</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>231</v>
+        <v>301</v>
       </c>
       <c r="H21" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K21" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L21" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M21" t="n">
-        <v>6400</v>
+        <v>14700</v>
       </c>
       <c r="N21" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>9037631490</v>
+        <v>19631522350</v>
       </c>
       <c r="P21" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-273000</v>
+        <v>1000</v>
       </c>
       <c r="S21" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>경영진 퇴출 요구 및 주가 조작 의혹 등 부정적인 여론이 지배적임. 실질적인 근거 제시 없이 불만과 의혹 제기가 대부분을 차지함.</t>
+          <t>LH 호남 반도체 설계 용역 발주 및 수주 기사 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가조작', '외국인', '김동선']</t>
+          <t>['수주', '반도체', '설계용역']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12330</v>
+        <v>12360</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.37%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.22</v>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H22" t="n">
         <v>0.14</v>
@@ -2450,7 +2450,7 @@
         <v>0.36</v>
       </c>
       <c r="O22" t="n">
-        <v>54817417760</v>
+        <v>55249908820</v>
       </c>
       <c r="P22" t="n">
         <v>20850</v>
@@ -2510,13 +2510,13 @@
         <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H23" t="n">
         <v>4.91</v>
@@ -2542,7 +2542,7 @@
         <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>5531431540</v>
+        <v>5668695162</v>
       </c>
       <c r="P23" t="n">
         <v>2705</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3640</v>
+        <v>3635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.54</v>
       </c>
       <c r="E24" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H24" t="n">
         <v>1.54</v>
@@ -2634,7 +2634,7 @@
         <v>2.08</v>
       </c>
       <c r="O24" t="n">
-        <v>43517772876</v>
+        <v>43846127426</v>
       </c>
       <c r="P24" t="n">
         <v>4335</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29250</v>
+        <v>29200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-5.95%</t>
+          <t>-6.11%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>42</v>
       </c>
       <c r="G25" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H25" t="n">
         <v>12.31</v>
@@ -2726,7 +2726,7 @@
         <v>12.14</v>
       </c>
       <c r="O25" t="n">
-        <v>45781362575</v>
+        <v>47040204400</v>
       </c>
       <c r="P25" t="n">
         <v>75900</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28050</v>
+        <v>27950</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.43%</t>
+          <t>-7.76%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.02</v>
       </c>
       <c r="E26" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F26" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G26" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>104898164475</v>
+        <v>106107249825</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>수면무호흡증 관련 뉴스가 있으나, 계단식 하락 추세 및 저점 지속 하락에 대한 우려가 큼. 주포 이탈 및 투자자들의 부정적인 전망이 우세함.</t>
+          <t>의료기기 신규 상장주, 호재에도 불구하고 계단식 하락 및 매도 압력.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['계단식 하락', '수면무호흡증', '주포']</t>
+          <t>['신규상장', '의료기기', '계단식하락']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-42.34%</t>
+          <t>-44.35%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>-0.32</v>
       </c>
       <c r="E27" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F27" t="n">
         <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>
@@ -2910,7 +2910,7 @@
         <v>6.18</v>
       </c>
       <c r="O27" t="n">
-        <v>656001721</v>
+        <v>758211007</v>
       </c>
       <c r="P27" t="n">
         <v>901</v>

--- a/data/trending_integrated_20260910_11.xlsx
+++ b/data/trending_integrated_20260910_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4890</v>
+        <v>4830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+144.50%</t>
+          <t>+141.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F2" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G2" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>565000242276</v>
+        <v>566451775996</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 대상 업종 신재생에너지 관련 기대감. 스펙주 특성상 신중론.</t>
+          <t>합병 대상 업종 신재생에너지 관련 기대. 높은 상승 가능성 언급되나, 스팩주 특성상 관망 필요.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스펙주', '신재생에너지', '합병']</t>
+          <t>['스팩주', '신재생에너지', '합병']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -676,7 +676,7 @@
         <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" t="n">
         <v>0.07000000000000001</v>
@@ -747,254 +747,254 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15120</v>
+        <v>29400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+25.06%</t>
+          <t>+26.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>322</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>198</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>371</v>
+        <v>76</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03</v>
+        <v>7.54</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12090</v>
+        <v>23200</v>
       </c>
       <c r="K4" t="n">
-        <v>12730</v>
+        <v>26900</v>
       </c>
       <c r="L4" t="n">
-        <v>15710</v>
+        <v>30150</v>
       </c>
       <c r="M4" t="n">
-        <v>12720</v>
+        <v>24500</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>260338661495</v>
+        <v>37131604925</v>
       </c>
       <c r="P4" t="n">
-        <v>36200</v>
+        <v>34750</v>
       </c>
       <c r="Q4" t="n">
-        <v>8920</v>
+        <v>20450</v>
       </c>
       <c r="R4" t="n">
-        <v>22000</v>
+        <v>-47000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>이란발 긴장 고조 및 유가 급등에 따른 폭발적 상승 기대. 거래량 증가.</t>
+          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '이란', '폭등']</t>
+          <t>['자사주', '소각', '주주환원']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28850</v>
+        <v>15110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+24.35%</t>
+          <t>+24.98%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>324</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>376</v>
       </c>
       <c r="H5" t="n">
-        <v>7.54</v>
+        <v>0.03</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23200</v>
+        <v>12090</v>
       </c>
       <c r="K5" t="n">
-        <v>26900</v>
+        <v>12730</v>
       </c>
       <c r="L5" t="n">
-        <v>30150</v>
+        <v>15710</v>
       </c>
       <c r="M5" t="n">
-        <v>24500</v>
+        <v>12720</v>
       </c>
       <c r="N5" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>36672708875</v>
+        <v>260894163580</v>
       </c>
       <c r="P5" t="n">
-        <v>34750</v>
+        <v>36200</v>
       </c>
       <c r="Q5" t="n">
-        <v>20450</v>
+        <v>8920</v>
       </c>
       <c r="R5" t="n">
-        <v>-47000</v>
+        <v>22000</v>
       </c>
       <c r="S5" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
+          <t>지정학적 리스크 고조에 따른 유가 급등 기대. 상한가 마감 및 단기 급등 가능성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주', '소각', '주주환원']</t>
+          <t>['유가', '이란', '급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13590</v>
+        <v>3660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.66%</t>
+          <t>+17.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H6" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11550</v>
+        <v>3105</v>
       </c>
       <c r="K6" t="n">
-        <v>11780</v>
+        <v>3170</v>
       </c>
       <c r="L6" t="n">
-        <v>14880</v>
+        <v>3775</v>
       </c>
       <c r="M6" t="n">
-        <v>11700</v>
+        <v>3165</v>
       </c>
       <c r="N6" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>87782617785</v>
+        <v>20511235249</v>
       </c>
       <c r="P6" t="n">
-        <v>33575</v>
+        <v>20800</v>
       </c>
       <c r="Q6" t="n">
-        <v>9690</v>
+        <v>1700</v>
       </c>
       <c r="R6" t="n">
-        <v>-78000</v>
+        <v>16000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['목표가', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3600</v>
+        <v>13540</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+15.94%</t>
+          <t>+17.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3105</v>
+        <v>11550</v>
       </c>
       <c r="K7" t="n">
-        <v>3170</v>
+        <v>11780</v>
       </c>
       <c r="L7" t="n">
-        <v>3775</v>
+        <v>14880</v>
       </c>
       <c r="M7" t="n">
-        <v>3165</v>
+        <v>11700</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O7" t="n">
-        <v>20120036970</v>
+        <v>88160179190</v>
       </c>
       <c r="P7" t="n">
-        <v>20800</v>
+        <v>33575</v>
       </c>
       <c r="Q7" t="n">
-        <v>1700</v>
+        <v>9690</v>
       </c>
       <c r="R7" t="n">
-        <v>16000</v>
+        <v>-78000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['목표가', '단기과열', '주가조작']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+13.58%</t>
+          <t>+13.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H8" t="n">
         <v>2.12</v>
@@ -1162,7 +1162,7 @@
         <v>2.07</v>
       </c>
       <c r="O8" t="n">
-        <v>168048152953</v>
+        <v>168800798646</v>
       </c>
       <c r="P8" t="n">
         <v>4795</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 매수세 속 단기 상승 기대감. 120일선 돌파 전망.</t>
+          <t>외인 매수세 지속 속 단기 급등 기대. 120일선 돌파 가능성 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['120일선', '외인']</t>
+          <t>['120일선', '외인', '급등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8300</v>
+        <v>8290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+11.73%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" t="n">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="H9" t="n">
         <v>1.17</v>
@@ -1254,7 +1254,7 @@
         <v>0.77</v>
       </c>
       <c r="O9" t="n">
-        <v>59984693265</v>
+        <v>60389744135</v>
       </c>
       <c r="P9" t="n">
         <v>21500</v>
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+4.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
         <v>28</v>
@@ -1346,7 +1346,7 @@
         <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>7397205472</v>
+        <v>7426290394</v>
       </c>
       <c r="P10" t="n">
         <v>2610</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3895</v>
+        <v>2145</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+2.88%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.62</v>
+        <v>0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
         <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="H11" t="n">
-        <v>1.57</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3810</v>
+        <v>2085</v>
       </c>
       <c r="K11" t="n">
-        <v>3870</v>
+        <v>2255</v>
       </c>
       <c r="L11" t="n">
-        <v>4250</v>
+        <v>2395</v>
       </c>
       <c r="M11" t="n">
-        <v>3660</v>
+        <v>2040</v>
       </c>
       <c r="N11" t="n">
-        <v>3.19</v>
+        <v>0.51</v>
       </c>
       <c r="O11" t="n">
-        <v>123782183524</v>
+        <v>17746156184</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>2930</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>910</v>
       </c>
       <c r="R11" t="n">
-        <v>-540000</v>
+        <v>-175000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
+          <t>새만금 사업 및 LH 관련 계약 추정. 외국인 및 기타 법인의 지속적인 매수세 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['투경', '6G', '장기전']</t>
+          <t>['새만금', 'LH', '매수세']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2130</v>
+        <v>3865</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.34</v>
+        <v>-1.62</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2085</v>
+        <v>3810</v>
       </c>
       <c r="K12" t="n">
-        <v>2255</v>
+        <v>3870</v>
       </c>
       <c r="L12" t="n">
-        <v>2395</v>
+        <v>4250</v>
       </c>
       <c r="M12" t="n">
-        <v>2040</v>
+        <v>3660</v>
       </c>
       <c r="N12" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="O12" t="n">
-        <v>17658449160</v>
+        <v>124226604903</v>
       </c>
       <c r="P12" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>-175000</v>
+        <v>-540000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>새만금 사업 및 LH 관련 계약 추정. 외국인 및 기타 법인의 지속적인 매수세 확인.</t>
+          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['새만금', 'LH', '매수세']</t>
+          <t>['투경', '6G', '장기전']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1850000</v>
+        <v>1853000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="F13" t="n">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G13" t="n">
-        <v>1628</v>
+        <v>1655</v>
       </c>
       <c r="H13" t="n">
         <v>50.67</v>
@@ -1622,7 +1622,7 @@
         <v>50.66</v>
       </c>
       <c r="O13" t="n">
-        <v>2881254072000</v>
+        <v>2915087921500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자사주 소각 및 ADR 상승에도 불구하고 매도 폭탄 및 패닉셀 우려.</t>
+          <t>대규모 자사주 소각 및 ADR 강세에 따른 반등 기대. 500만 목표가 및 오후 급등 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주소각', 'ADR', '패닉셀']</t>
+          <t>['자사주', 'ADR', '반등']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>152100</v>
+        <v>152400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F14" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G14" t="n">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="H14" t="n">
         <v>15.65</v>
@@ -1714,7 +1714,7 @@
         <v>15.25</v>
       </c>
       <c r="O14" t="n">
-        <v>304937284400</v>
+        <v>305856269700</v>
       </c>
       <c r="P14" t="n">
         <v>164700</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유가 폭등 수혜 기대감 속 개인 투자자 우려. JP모건 대량매수 패턴 분석.</t>
+          <t>유가 급등에 따른 수혜 기대감. 전고점 돌파 및 단기 하락 가능성 공존.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가폭등', 'JP모건', '수익']</t>
+          <t>['유가', '전고점', '수혜']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>266000</v>
+        <v>266750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.30%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F15" t="n">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="G15" t="n">
-        <v>1258</v>
+        <v>1237</v>
       </c>
       <c r="H15" t="n">
         <v>46.81</v>
@@ -1806,7 +1806,7 @@
         <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1681300955750</v>
+        <v>1707759620250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 매입 리스크 및 매도 의견 다수. 코스피 폭락 및 급락 예상.</t>
+          <t>하이닉스 대비 상대적 부진, 자사주 매입 리스크 및 매도 의견 다수. 급락 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주매입', '매도', '폭락']</t>
+          <t>['삼성전자', '하이닉스', '매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14070</v>
+        <v>14080</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="H16" t="n">
         <v>6.09</v>
@@ -1898,7 +1898,7 @@
         <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>90891616800</v>
+        <v>91382104330</v>
       </c>
       <c r="P16" t="n">
         <v>30200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 소식 기반 상승 기대. 공매도 금지 관련 언급.</t>
+          <t>미국 원전 건설 계획 및 공매도 금지 기대감. 양전 및 상승 전망, 추매 의견.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '건설']</t>
+          <t>['원전', '공매도', '상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,18 +1947,18 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18960</v>
+        <v>18950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" t="n">
         <v>48</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>63854324265</v>
+        <v>64453698895</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88900</v>
+        <v>89000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F18" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G18" t="n">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2082,7 +2082,7 @@
         <v>23.61</v>
       </c>
       <c r="O18" t="n">
-        <v>120616112800</v>
+        <v>121642100250</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14400</v>
+        <v>15100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>404</v>
+        <v>302</v>
       </c>
       <c r="H19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14960</v>
+        <v>15640</v>
       </c>
       <c r="K19" t="n">
-        <v>15040</v>
+        <v>15600</v>
       </c>
       <c r="L19" t="n">
-        <v>15040</v>
+        <v>15600</v>
       </c>
       <c r="M19" t="n">
-        <v>14190</v>
+        <v>14700</v>
       </c>
       <c r="N19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>73352567185</v>
+        <v>20117293525</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>1263</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-492000</v>
+        <v>1000</v>
       </c>
       <c r="S19" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세 속 국내 동반 상승 기대. 외인 매수세 변화 관찰.</t>
+          <t>LH 호남 반도체 설계 용역 발주 및 수주 기사 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외국인']</t>
+          <t>['수주', '반도체', '설계용역']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6600</v>
+        <v>14400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.03</v>
+        <v>1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>408</v>
       </c>
       <c r="H20" t="n">
-        <v>15.68</v>
+        <v>2.89</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6860</v>
+        <v>14960</v>
       </c>
       <c r="K20" t="n">
-        <v>6800</v>
+        <v>15040</v>
       </c>
       <c r="L20" t="n">
-        <v>6820</v>
+        <v>15040</v>
       </c>
       <c r="M20" t="n">
-        <v>6400</v>
+        <v>14190</v>
       </c>
       <c r="N20" t="n">
-        <v>16.71</v>
+        <v>1.55</v>
       </c>
       <c r="O20" t="n">
-        <v>9511142180</v>
+        <v>73587819150</v>
       </c>
       <c r="P20" t="n">
-        <v>13000</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>6030</v>
+        <v>1263</v>
       </c>
       <c r="R20" t="n">
-        <v>-273000</v>
+        <v>-492000</v>
       </c>
       <c r="S20" t="n">
-        <v>-10000</v>
+        <v>-7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>경영진 퇴출 요구 및 주가 조작 의혹 등 부정적인 여론이 지배적임. 실질적인 근거 제시 없이 불만과 의혹 제기가 대부분을 차지함.</t>
+          <t>미국 광통신주 강세 및 AI 관련주 부각. 외인 매수세 유입 및 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가조작', '외국인', '김동선']</t>
+          <t>['광통신', 'AI', '외인']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14960</v>
+        <v>6580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.35%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="E21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15640</v>
+        <v>6860</v>
       </c>
       <c r="K21" t="n">
-        <v>15600</v>
+        <v>6800</v>
       </c>
       <c r="L21" t="n">
-        <v>15600</v>
+        <v>6820</v>
       </c>
       <c r="M21" t="n">
-        <v>14700</v>
+        <v>6400</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>16.71</v>
       </c>
       <c r="O21" t="n">
-        <v>19631522350</v>
+        <v>9654787050</v>
       </c>
       <c r="P21" t="n">
-        <v>19380</v>
+        <v>13000</v>
       </c>
       <c r="Q21" t="n">
-        <v>3200</v>
+        <v>6030</v>
       </c>
       <c r="R21" t="n">
-        <v>1000</v>
+        <v>-273000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>LH 호남 반도체 설계 용역 발주 및 수주 기사 기반 상승 기대.</t>
+          <t>자사주 소각 기대감 대비 외인 매도세 및 부정적 의견. 주가 조작 및 잡주 인식.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주', '반도체', '설계용역']</t>
+          <t>['자사주', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12360</v>
+        <v>12370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.14%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.22</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G22" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H22" t="n">
         <v>0.14</v>
@@ -2450,7 +2450,7 @@
         <v>0.36</v>
       </c>
       <c r="O22" t="n">
-        <v>55249908820</v>
+        <v>55360856740</v>
       </c>
       <c r="P22" t="n">
         <v>20850</v>
@@ -2495,162 +2495,162 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2135</v>
+        <v>3655</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="E23" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>1.54</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2260</v>
+        <v>3865</v>
       </c>
       <c r="K23" t="n">
-        <v>2250</v>
+        <v>3845</v>
       </c>
       <c r="L23" t="n">
-        <v>2290</v>
+        <v>4075</v>
       </c>
       <c r="M23" t="n">
-        <v>2080</v>
+        <v>3605</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>2.08</v>
       </c>
       <c r="O23" t="n">
-        <v>5668695162</v>
+        <v>44003733706</v>
       </c>
       <c r="P23" t="n">
-        <v>2705</v>
+        <v>4335</v>
       </c>
       <c r="Q23" t="n">
-        <v>1418</v>
+        <v>1246</v>
       </c>
       <c r="R23" t="n">
-        <v>-133000</v>
+        <v>-210000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 이슈 및 새 최대주주 등장으로 인한 경영권 분쟁 가능성. 단기 급등락 예상.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '경영권 분쟁', '최대주주']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3635</v>
+        <v>29300</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.95%</t>
+          <t>-5.79%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.54</v>
+        <v>0.17</v>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>12.31</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3865</v>
+        <v>31100</v>
       </c>
       <c r="K24" t="n">
-        <v>3845</v>
+        <v>30450</v>
       </c>
       <c r="L24" t="n">
-        <v>4075</v>
+        <v>30600</v>
       </c>
       <c r="M24" t="n">
-        <v>3605</v>
+        <v>28800</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>12.14</v>
       </c>
       <c r="O24" t="n">
-        <v>43846127426</v>
+        <v>47275938900</v>
       </c>
       <c r="P24" t="n">
-        <v>4335</v>
+        <v>75900</v>
       </c>
       <c r="Q24" t="n">
-        <v>1246</v>
+        <v>15000</v>
       </c>
       <c r="R24" t="n">
-        <v>-210000</v>
+        <v>-343000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29200</v>
+        <v>2125</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.11%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.17</v>
+        <v>-0.35</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="H25" t="n">
-        <v>12.31</v>
+        <v>4.91</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,47 +2711,47 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>31100</v>
+        <v>2260</v>
       </c>
       <c r="K25" t="n">
-        <v>30450</v>
+        <v>2250</v>
       </c>
       <c r="L25" t="n">
-        <v>30600</v>
+        <v>2290</v>
       </c>
       <c r="M25" t="n">
-        <v>28800</v>
+        <v>2080</v>
       </c>
       <c r="N25" t="n">
-        <v>12.14</v>
+        <v>5.26</v>
       </c>
       <c r="O25" t="n">
-        <v>47040204400</v>
+        <v>5729328262</v>
       </c>
       <c r="P25" t="n">
-        <v>75900</v>
+        <v>2705</v>
       </c>
       <c r="Q25" t="n">
-        <v>15000</v>
+        <v>1418</v>
       </c>
       <c r="R25" t="n">
-        <v>-343000</v>
+        <v>-133000</v>
       </c>
       <c r="S25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>M&amp;A 관련 기대감 속 신규 대주주 등장. 단기 변동성 및 하락 가능성 혼재.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['M&amp;A', '대주주', '변동성']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -2789,10 +2789,10 @@
         <v>187</v>
       </c>
       <c r="F26" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G26" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>106107249825</v>
+        <v>106356187125</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2878,13 +2878,13 @@
         <v>-0.32</v>
       </c>
       <c r="E27" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G27" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>

--- a/data/trending_integrated_20260910_11.xlsx
+++ b/data/trending_integrated_20260910_11.xlsx
@@ -567,21 +567,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4830</v>
+        <v>4685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+141.50%</t>
+          <t>+134.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="F2" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G2" t="n">
         <v>287</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>566451775996</v>
+        <v>573875514794</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 대상 업종 신재생에너지 관련 기대. 높은 상승 가능성 언급되나, 스팩주 특성상 관망 필요.</t>
+          <t>신재생에너지 업종 합병 기대감 속 스팩주 시세 분출 가능성. 개인 투자자 쏠림 현상 주의.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '신재생에너지', '합병']</t>
+          <t>['엔에이치스팩34호', '스팩주', '합병']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,10 +670,10 @@
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
         <v>40</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29400</v>
+        <v>29200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+26.72%</t>
+          <t>+25.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H4" t="n">
         <v>7.54</v>
@@ -794,7 +794,7 @@
         <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>37131604925</v>
+        <v>38455685600</v>
       </c>
       <c r="P4" t="n">
         <v>34750</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15110</v>
+        <v>14980</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+24.98%</t>
+          <t>+23.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>260894163580</v>
+        <v>262867636070</v>
       </c>
       <c r="P5" t="n">
         <v>36200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>지정학적 리스크 고조에 따른 유가 급등 기대. 상한가 마감 및 단기 급등 가능성.</t>
+          <t>지정학적 리스크 부각에 따른 유가 급등 및 흥구석유 상한가 기대감. 거래량 및 프로그램 매수세 주목.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '이란', '급등']</t>
+          <t>['흥구석유', '유가 급등', '상한가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>20511235249</v>
+        <v>21352907309</v>
       </c>
       <c r="P6" t="n">
         <v>20800</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13540</v>
+        <v>13430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+17.23%</t>
+          <t>+16.28%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1070,7 +1070,7 @@
         <v>4.63</v>
       </c>
       <c r="O7" t="n">
-        <v>88160179190</v>
+        <v>88827914670</v>
       </c>
       <c r="P7" t="n">
         <v>33575</v>
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1997</v>
+        <v>8520</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+13.47%</t>
+          <t>+14.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
-        <v>116</v>
+        <v>1107</v>
       </c>
       <c r="H8" t="n">
-        <v>2.12</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1760</v>
+        <v>7420</v>
       </c>
       <c r="K8" t="n">
-        <v>1782</v>
+        <v>8000</v>
       </c>
       <c r="L8" t="n">
-        <v>2200</v>
+        <v>9100</v>
       </c>
       <c r="M8" t="n">
-        <v>1772</v>
+        <v>7930</v>
       </c>
       <c r="N8" t="n">
-        <v>2.07</v>
+        <v>0.77</v>
       </c>
       <c r="O8" t="n">
-        <v>168800798646</v>
+        <v>61453712575</v>
       </c>
       <c r="P8" t="n">
-        <v>4795</v>
+        <v>21500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1524</v>
+        <v>2300</v>
       </c>
       <c r="R8" t="n">
-        <v>-706000</v>
+        <v>117000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 매수세 지속 속 단기 급등 기대. 120일선 돌파 가능성 제기.</t>
+          <t>폐암학회 발표 및 신약 임상 결과에 따른 기술 이전 기대감. FDA 2상 승인 및 5연상 목표.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['120일선', '외인', '급등']</t>
+          <t>['페니트리움바이오', '신약', 'FDA']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8290</v>
+        <v>1962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+11.73%</t>
+          <t>+11.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>216</v>
+        <v>104</v>
       </c>
       <c r="F9" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>1120</v>
+        <v>112</v>
       </c>
       <c r="H9" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7420</v>
+        <v>1760</v>
       </c>
       <c r="K9" t="n">
-        <v>8000</v>
+        <v>1782</v>
       </c>
       <c r="L9" t="n">
-        <v>9100</v>
+        <v>2200</v>
       </c>
       <c r="M9" t="n">
-        <v>7930</v>
+        <v>1772</v>
       </c>
       <c r="N9" t="n">
-        <v>0.77</v>
+        <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>60389744135</v>
+        <v>172755440730</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>4795</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>1524</v>
       </c>
       <c r="R9" t="n">
-        <v>117000</v>
+        <v>-706000</v>
       </c>
       <c r="S9" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>세계 최초 항암제 내성 극복 관련 글로벌 학회 참여 및 기술 이전 가능성. 4연상 이상 기대감 고조.</t>
+          <t>외국인 순매수세 속 단기 급등 기대감. 단, 매물 소화 및 추세 전환 여부 주목.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['항암제', '내성 극복', '기술 이전']</t>
+          <t>['외국인', '매수세', '급등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.13%</t>
+          <t>+2.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10" t="n">
         <v>28</v>
@@ -1346,7 +1346,7 @@
         <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>7426290394</v>
+        <v>7497852576</v>
       </c>
       <c r="P10" t="n">
         <v>2610</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2145</v>
+        <v>3910</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.88%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>-1.62</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="H11" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2085</v>
+        <v>3810</v>
       </c>
       <c r="K11" t="n">
-        <v>2255</v>
+        <v>3870</v>
       </c>
       <c r="L11" t="n">
-        <v>2395</v>
+        <v>4250</v>
       </c>
       <c r="M11" t="n">
-        <v>2040</v>
+        <v>3660</v>
       </c>
       <c r="N11" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="O11" t="n">
-        <v>17746156184</v>
+        <v>125425666454</v>
       </c>
       <c r="P11" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-175000</v>
+        <v>-540000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>새만금 사업 및 LH 관련 계약 추정. 외국인 및 기타 법인의 지속적인 매수세 확인.</t>
+          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['새만금', 'LH', '매수세']</t>
+          <t>['투경', '6G', '장기전']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3865</v>
+        <v>2112</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.29%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.62</v>
+        <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="H12" t="n">
-        <v>1.57</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3810</v>
+        <v>2085</v>
       </c>
       <c r="K12" t="n">
-        <v>3870</v>
+        <v>2255</v>
       </c>
       <c r="L12" t="n">
-        <v>4250</v>
+        <v>2395</v>
       </c>
       <c r="M12" t="n">
-        <v>3660</v>
+        <v>2040</v>
       </c>
       <c r="N12" t="n">
-        <v>3.19</v>
+        <v>0.51</v>
       </c>
       <c r="O12" t="n">
-        <v>124226604903</v>
+        <v>17953535553</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>2930</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>910</v>
       </c>
       <c r="R12" t="n">
-        <v>-540000</v>
+        <v>-175000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
+          <t>주요 사업 관련 소식과 함께 기타 법인 및 외국인 순매수세 유입. 주가 바닥 다지기 및 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['투경', '6G', '장기전']</t>
+          <t>['강동씨앤엘', '기타법인', '순매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,82 +1563,82 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1853000</v>
+        <v>14340</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
       <c r="E13" t="n">
-        <v>793</v>
+        <v>89</v>
       </c>
       <c r="F13" t="n">
-        <v>459</v>
+        <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>1655</v>
+        <v>438</v>
       </c>
       <c r="H13" t="n">
-        <v>50.67</v>
+        <v>6.09</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1856000</v>
+        <v>14320</v>
       </c>
       <c r="K13" t="n">
-        <v>1879000</v>
+        <v>13800</v>
       </c>
       <c r="L13" t="n">
-        <v>1890000</v>
+        <v>14400</v>
       </c>
       <c r="M13" t="n">
-        <v>1811000</v>
+        <v>13260</v>
       </c>
       <c r="N13" t="n">
-        <v>50.66</v>
+        <v>5.64</v>
       </c>
       <c r="O13" t="n">
-        <v>2915087921500</v>
+        <v>101252480480</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>30200</v>
       </c>
       <c r="Q13" t="n">
-        <v>293000</v>
+        <v>3540</v>
       </c>
       <c r="R13" t="n">
-        <v>-110000</v>
+        <v>-132000</v>
       </c>
       <c r="S13" t="n">
-        <v>-78000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대규모 자사주 소각 및 ADR 강세에 따른 반등 기대. 500만 목표가 및 오후 급등 전망.</t>
+          <t>미국 원전 건설 계획 및 공매도 금지 기대감. 양전 및 상승 전망, 추매 의견.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주', 'ADR', '반등']</t>
+          <t>['원전', '공매도', '상승']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>152400</v>
+        <v>1856000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>333</v>
+        <v>799</v>
       </c>
       <c r="F14" t="n">
-        <v>156</v>
+        <v>457</v>
       </c>
       <c r="G14" t="n">
-        <v>850</v>
+        <v>1743</v>
       </c>
       <c r="H14" t="n">
-        <v>15.65</v>
+        <v>50.67</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>153500</v>
+        <v>1856000</v>
       </c>
       <c r="K14" t="n">
-        <v>155500</v>
+        <v>1879000</v>
       </c>
       <c r="L14" t="n">
-        <v>164700</v>
+        <v>1890000</v>
       </c>
       <c r="M14" t="n">
-        <v>151200</v>
+        <v>1811000</v>
       </c>
       <c r="N14" t="n">
-        <v>15.25</v>
+        <v>50.66</v>
       </c>
       <c r="O14" t="n">
-        <v>305856269700</v>
+        <v>3022214445500</v>
       </c>
       <c r="P14" t="n">
-        <v>164700</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>87700</v>
+        <v>293000</v>
       </c>
       <c r="R14" t="n">
-        <v>104000</v>
+        <v>-110000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유가 급등에 따른 수혜 기대감. 전고점 돌파 및 단기 하락 가능성 공존.</t>
+          <t>자사주 소각 및 리밸런싱 효과 기대감 속 SK하이닉스 반등 전망. ADR과의 연동성 및 단기 급등 가능성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가', '전고점', '수혜']</t>
+          <t>['SK하이닉스', '자사주 소각', '반등']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>266750</v>
+        <v>267250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="F15" t="n">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G15" t="n">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="H15" t="n">
         <v>46.81</v>
@@ -1806,7 +1806,7 @@
         <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1707759620250</v>
+        <v>1744771683750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>하이닉스 대비 상대적 부진, 자사주 매입 리스크 및 매도 의견 다수. 급락 우려.</t>
+          <t>삼성전자 주가 부진에 대한 부정적 전망. 자사주 매입 및 매크로 변수 불확실성 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['삼성전자', '하이닉스', '매도']</t>
+          <t>['삼성전자', '주가 부진', '자사주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14080</v>
+        <v>151000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E16" t="n">
-        <v>86</v>
+        <v>336</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="G16" t="n">
-        <v>425</v>
+        <v>855</v>
       </c>
       <c r="H16" t="n">
-        <v>6.09</v>
+        <v>15.65</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14320</v>
+        <v>153500</v>
       </c>
       <c r="K16" t="n">
-        <v>13800</v>
+        <v>155500</v>
       </c>
       <c r="L16" t="n">
-        <v>14190</v>
+        <v>164700</v>
       </c>
       <c r="M16" t="n">
-        <v>13260</v>
+        <v>150700</v>
       </c>
       <c r="N16" t="n">
-        <v>5.64</v>
+        <v>15.25</v>
       </c>
       <c r="O16" t="n">
-        <v>91382104330</v>
+        <v>310525197050</v>
       </c>
       <c r="P16" t="n">
-        <v>30200</v>
+        <v>164700</v>
       </c>
       <c r="Q16" t="n">
-        <v>3540</v>
+        <v>87700</v>
       </c>
       <c r="R16" t="n">
-        <v>-132000</v>
+        <v>104000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 원전 건설 계획 및 공매도 금지 기대감. 양전 및 상승 전망, 추매 의견.</t>
+          <t>유가 급등 수혜 기대감과 함께 주가 하락 및 변동성 확대. 단기 차익 실현 및 홀딩 전략 분분.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '상승']</t>
+          <t>['SK이노베이션', '유가', '주가 하락']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18950</v>
+        <v>19020</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>64453698895</v>
+        <v>66042079230</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 투자 관련 긍정적 기대감 속 급락 마감. 중동전쟁 악재 영향 없다는 의견과 하락 전망 혼재.</t>
+          <t>미국 투자 관련 기대감과 함께 중동 지정학적 리스크 속 주가 변동성 확대. 대차 거래 내역 주목.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['미국투자', '중동전쟁', '급락']</t>
+          <t>['대우건설', '미국 투자', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>89000</v>
+        <v>89200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F18" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G18" t="n">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2082,7 +2082,7 @@
         <v>23.61</v>
       </c>
       <c r="O18" t="n">
-        <v>121642100250</v>
+        <v>124153359950</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15100</v>
+        <v>14440</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>-3.48%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G19" t="n">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15640</v>
+        <v>14960</v>
       </c>
       <c r="K19" t="n">
-        <v>15600</v>
+        <v>15040</v>
       </c>
       <c r="L19" t="n">
-        <v>15600</v>
+        <v>15040</v>
       </c>
       <c r="M19" t="n">
-        <v>14700</v>
+        <v>14190</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O19" t="n">
-        <v>20117293525</v>
+        <v>74184411575</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>1263</v>
       </c>
       <c r="R19" t="n">
-        <v>1000</v>
+        <v>-492000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>LH 호남 반도체 설계 용역 발주 및 수주 기사 기반 상승 기대.</t>
+          <t>미국 광통신주 강세 속 국내 동반 상승 기대. 외인 매수세 변화 관찰.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['수주', '반도체', '설계용역']</t>
+          <t>['광통신', 'AI', '외국인']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14400</v>
+        <v>6600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.34</v>
+        <v>-1.03</v>
       </c>
       <c r="E20" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>408</v>
+        <v>256</v>
       </c>
       <c r="H20" t="n">
-        <v>2.89</v>
+        <v>15.68</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>14960</v>
+        <v>6860</v>
       </c>
       <c r="K20" t="n">
-        <v>15040</v>
+        <v>6800</v>
       </c>
       <c r="L20" t="n">
-        <v>15040</v>
+        <v>6820</v>
       </c>
       <c r="M20" t="n">
-        <v>14190</v>
+        <v>6400</v>
       </c>
       <c r="N20" t="n">
-        <v>1.55</v>
+        <v>16.71</v>
       </c>
       <c r="O20" t="n">
-        <v>73587819150</v>
+        <v>10010240150</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>13000</v>
       </c>
       <c r="Q20" t="n">
-        <v>1263</v>
+        <v>6030</v>
       </c>
       <c r="R20" t="n">
-        <v>-492000</v>
+        <v>-273000</v>
       </c>
       <c r="S20" t="n">
-        <v>-7000</v>
+        <v>-10000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세 및 AI 관련주 부각. 외인 매수세 유입 및 상승 추세 전망.</t>
+          <t>자사주 소각 기대감 대비 외인 매도세 및 부정적 의견. 주가 조작 및 잡주 인식.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인']</t>
+          <t>['자사주', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6580</v>
+        <v>15000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>-4.09%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G21" t="n">
-        <v>252</v>
+        <v>303</v>
       </c>
       <c r="H21" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K21" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L21" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M21" t="n">
-        <v>6400</v>
+        <v>14700</v>
       </c>
       <c r="N21" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>9654787050</v>
+        <v>20607590705</v>
       </c>
       <c r="P21" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-273000</v>
+        <v>1000</v>
       </c>
       <c r="S21" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>자사주 소각 기대감 대비 외인 매도세 및 부정적 의견. 주가 조작 및 잡주 인식.</t>
+          <t>LH 호남 반도체 설계 용역 발주 및 수주 기사 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['자사주', '외인', '주가조작']</t>
+          <t>['수주', '반도체', '설계용역']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,99 +2396,99 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12370</v>
+        <v>2150</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.07%</t>
+          <t>-4.87%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F22" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="H22" t="n">
-        <v>0.14</v>
+        <v>4.91</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>13030</v>
+        <v>2260</v>
       </c>
       <c r="K22" t="n">
-        <v>13160</v>
+        <v>2250</v>
       </c>
       <c r="L22" t="n">
-        <v>13240</v>
+        <v>2290</v>
       </c>
       <c r="M22" t="n">
-        <v>12150</v>
+        <v>2080</v>
       </c>
       <c r="N22" t="n">
-        <v>0.36</v>
+        <v>5.26</v>
       </c>
       <c r="O22" t="n">
-        <v>55360856740</v>
+        <v>5767823432</v>
       </c>
       <c r="P22" t="n">
-        <v>20850</v>
+        <v>2705</v>
       </c>
       <c r="Q22" t="n">
-        <v>4020</v>
+        <v>1418</v>
       </c>
       <c r="R22" t="n">
-        <v>25000</v>
+        <v>-133000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
+          <t>M&amp;A 관련 기대감 속 최대주주 변경 및 경영권 분쟁 가능성. 신규 유증 발표 예정.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['호재', '원전', '하락']</t>
+          <t>['써니전자', 'M&amp;A', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3655</v>
+        <v>3660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.43%</t>
+          <t>-5.30%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.54</v>
       </c>
       <c r="E23" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F23" t="n">
         <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H23" t="n">
         <v>1.54</v>
@@ -2542,7 +2542,7 @@
         <v>2.08</v>
       </c>
       <c r="O23" t="n">
-        <v>44003733706</v>
+        <v>44536104332</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>
@@ -2587,70 +2587,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29300</v>
+        <v>12320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.79%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.17</v>
+        <v>-0.22</v>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="H24" t="n">
-        <v>12.31</v>
+        <v>0.14</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>31100</v>
+        <v>13030</v>
       </c>
       <c r="K24" t="n">
-        <v>30450</v>
+        <v>13160</v>
       </c>
       <c r="L24" t="n">
-        <v>30600</v>
+        <v>13240</v>
       </c>
       <c r="M24" t="n">
-        <v>28800</v>
+        <v>12150</v>
       </c>
       <c r="N24" t="n">
-        <v>12.14</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>47275938900</v>
+        <v>56166855075</v>
       </c>
       <c r="P24" t="n">
-        <v>75900</v>
+        <v>20850</v>
       </c>
       <c r="Q24" t="n">
-        <v>15000</v>
+        <v>4020</v>
       </c>
       <c r="R24" t="n">
-        <v>-343000</v>
+        <v>25000</v>
       </c>
       <c r="S24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['호재', '원전', '하락']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2125</v>
+        <v>29400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-5.97%</t>
+          <t>-5.47%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.35</v>
+        <v>0.17</v>
       </c>
       <c r="E25" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G25" t="n">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="H25" t="n">
-        <v>4.91</v>
+        <v>12.31</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,47 +2711,47 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2260</v>
+        <v>31100</v>
       </c>
       <c r="K25" t="n">
-        <v>2250</v>
+        <v>30450</v>
       </c>
       <c r="L25" t="n">
-        <v>2290</v>
+        <v>30600</v>
       </c>
       <c r="M25" t="n">
-        <v>2080</v>
+        <v>28800</v>
       </c>
       <c r="N25" t="n">
-        <v>5.26</v>
+        <v>12.14</v>
       </c>
       <c r="O25" t="n">
-        <v>5729328262</v>
+        <v>47987528675</v>
       </c>
       <c r="P25" t="n">
-        <v>2705</v>
+        <v>75900</v>
       </c>
       <c r="Q25" t="n">
-        <v>1418</v>
+        <v>15000</v>
       </c>
       <c r="R25" t="n">
-        <v>-133000</v>
+        <v>-343000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 기대감 속 신규 대주주 등장. 단기 변동성 및 하락 가능성 혼재.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['M&amp;A', '대주주', '변동성']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27950</v>
+        <v>28200</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.76%</t>
+          <t>-6.93%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.02</v>
       </c>
       <c r="E26" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F26" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G26" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>106356187125</v>
+        <v>107924506550</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2878,13 +2878,13 @@
         <v>-0.32</v>
       </c>
       <c r="E27" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>

--- a/data/trending_integrated_20260910_11.xlsx
+++ b/data/trending_integrated_20260910_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4685</v>
+        <v>4745</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+134.25%</t>
+          <t>+137.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="F2" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="G2" t="n">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>573875514794</v>
+        <v>589999855365</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신재생에너지 업종 합병 기대감 속 스팩주 시세 분출 가능성. 개인 투자자 쏠림 현상 주의.</t>
+          <t>합병 대상 업종(신재생에너지) 관련 언급 있으나, 스펙주 특성상 투자 주의 및 단기 변동성 경고.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['엔에이치스팩34호', '스팩주', '합병']</t>
+          <t>['스펙주', '신재생에너지', '단기 변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" t="n">
         <v>0.07000000000000001</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29200</v>
+        <v>29850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+25.86%</t>
+          <t>+28.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H4" t="n">
         <v>7.54</v>
@@ -794,7 +794,7 @@
         <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>38455685600</v>
+        <v>39574802475</v>
       </c>
       <c r="P4" t="n">
         <v>34750</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14980</v>
+        <v>14910</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+23.90%</t>
+          <t>+23.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="F5" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G5" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>262867636070</v>
+        <v>265385330580</v>
       </c>
       <c r="P5" t="n">
         <v>36200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>지정학적 리스크 부각에 따른 유가 급등 및 흥구석유 상한가 기대감. 거래량 및 프로그램 매수세 주목.</t>
+          <t>유가 급등 기대감과 함께 거래량 증가 및 상한가 마감 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['흥구석유', '유가 급등', '상한가']</t>
+          <t>['유가 급등', '거래량', '상한가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,70 +931,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3660</v>
+        <v>13350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.87%</t>
+          <t>+15.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3105</v>
+        <v>11550</v>
       </c>
       <c r="K6" t="n">
-        <v>3170</v>
+        <v>11780</v>
       </c>
       <c r="L6" t="n">
-        <v>3775</v>
+        <v>14880</v>
       </c>
       <c r="M6" t="n">
-        <v>3165</v>
+        <v>11700</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O6" t="n">
-        <v>21352907309</v>
+        <v>89903243495</v>
       </c>
       <c r="P6" t="n">
-        <v>20800</v>
+        <v>33575</v>
       </c>
       <c r="Q6" t="n">
-        <v>1700</v>
+        <v>9690</v>
       </c>
       <c r="R6" t="n">
-        <v>16000</v>
+        <v>-78000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['목표가', '단기과열', '주가조작']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13430</v>
+        <v>3550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+16.28%</t>
+          <t>+14.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H7" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11550</v>
+        <v>3105</v>
       </c>
       <c r="K7" t="n">
-        <v>11780</v>
+        <v>3170</v>
       </c>
       <c r="L7" t="n">
-        <v>14880</v>
+        <v>3775</v>
       </c>
       <c r="M7" t="n">
-        <v>11700</v>
+        <v>3165</v>
       </c>
       <c r="N7" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>88827914670</v>
+        <v>22116880042</v>
       </c>
       <c r="P7" t="n">
-        <v>33575</v>
+        <v>20800</v>
       </c>
       <c r="Q7" t="n">
-        <v>9690</v>
+        <v>1700</v>
       </c>
       <c r="R7" t="n">
-        <v>-78000</v>
+        <v>16000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['목표가', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8520</v>
+        <v>8350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+14.82%</t>
+          <t>+12.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F8" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G8" t="n">
-        <v>1107</v>
+        <v>1169</v>
       </c>
       <c r="H8" t="n">
         <v>1.17</v>
@@ -1162,7 +1162,7 @@
         <v>0.77</v>
       </c>
       <c r="O8" t="n">
-        <v>61453712575</v>
+        <v>62597827105</v>
       </c>
       <c r="P8" t="n">
         <v>21500</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+11.48%</t>
+          <t>+11.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="H9" t="n">
         <v>2.12</v>
@@ -1254,7 +1254,7 @@
         <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>172755440730</v>
+        <v>175459857411</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인 순매수세 속 단기 급등 기대감. 단, 매물 소화 및 추세 전환 여부 주목.</t>
+          <t>외국인 매수세 속 급등 기대감과 매도 물량 혼조세. 주포 개입 의혹 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외국인', '매수세', '급등']</t>
+          <t>['외국인', '매수세', '주포']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.95%</t>
+          <t>+2.56%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
         <v>59</v>
@@ -1346,7 +1346,7 @@
         <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>7497852576</v>
+        <v>7544090787</v>
       </c>
       <c r="P10" t="n">
         <v>2610</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3910</v>
+        <v>3885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-1.62</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="H11" t="n">
         <v>1.57</v>
@@ -1438,7 +1438,7 @@
         <v>3.19</v>
       </c>
       <c r="O11" t="n">
-        <v>125425666454</v>
+        <v>127297182385</v>
       </c>
       <c r="P11" t="n">
         <v>8100</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2112</v>
+        <v>2090</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F12" t="n">
         <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
         <v>0.85</v>
@@ -1530,7 +1530,7 @@
         <v>0.51</v>
       </c>
       <c r="O12" t="n">
-        <v>17953535553</v>
+        <v>18172610035</v>
       </c>
       <c r="P12" t="n">
         <v>2930</v>
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14340</v>
+        <v>1857000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>89</v>
+        <v>799</v>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>469</v>
       </c>
       <c r="G13" t="n">
-        <v>438</v>
+        <v>1815</v>
       </c>
       <c r="H13" t="n">
-        <v>6.09</v>
+        <v>50.67</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14320</v>
+        <v>1856000</v>
       </c>
       <c r="K13" t="n">
-        <v>13800</v>
+        <v>1879000</v>
       </c>
       <c r="L13" t="n">
-        <v>14400</v>
+        <v>1890000</v>
       </c>
       <c r="M13" t="n">
-        <v>13260</v>
+        <v>1811000</v>
       </c>
       <c r="N13" t="n">
-        <v>5.64</v>
+        <v>50.66</v>
       </c>
       <c r="O13" t="n">
-        <v>101252480480</v>
+        <v>3156446871500</v>
       </c>
       <c r="P13" t="n">
-        <v>30200</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3540</v>
+        <v>293000</v>
       </c>
       <c r="R13" t="n">
-        <v>-132000</v>
+        <v>-110000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전 건설 계획 및 공매도 금지 기대감. 양전 및 상승 전망, 추매 의견.</t>
+          <t>연기금 리밸런싱, 외인/기관 매수세 속 상승 추세 기대감. 폭등 전 조짐 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '상승']</t>
+          <t>['연기금', '외인 매수', '상승 추세']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1856000</v>
+        <v>14325</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
       <c r="E14" t="n">
-        <v>799</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
-        <v>457</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>1743</v>
+        <v>496</v>
       </c>
       <c r="H14" t="n">
-        <v>50.67</v>
+        <v>6.09</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1856000</v>
+        <v>14320</v>
       </c>
       <c r="K14" t="n">
-        <v>1879000</v>
+        <v>13800</v>
       </c>
       <c r="L14" t="n">
-        <v>1890000</v>
+        <v>14400</v>
       </c>
       <c r="M14" t="n">
-        <v>1811000</v>
+        <v>13260</v>
       </c>
       <c r="N14" t="n">
-        <v>50.66</v>
+        <v>5.64</v>
       </c>
       <c r="O14" t="n">
-        <v>3022214445500</v>
+        <v>110126377460</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>293000</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>-110000</v>
+        <v>-132000</v>
       </c>
       <c r="S14" t="n">
-        <v>-78000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>자사주 소각 및 리밸런싱 효과 기대감 속 SK하이닉스 반등 전망. ADR과의 연동성 및 단기 급등 가능성.</t>
+          <t>미국 신규 원전 건설 관련 모멘텀 및 공매도 금지 관련 언급, 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '자사주 소각', '반등']</t>
+          <t>['원전', '미국 건설', '공매도 금지']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>267250</v>
+        <v>152200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>792</v>
+        <v>347</v>
       </c>
       <c r="F15" t="n">
-        <v>464</v>
+        <v>164</v>
       </c>
       <c r="G15" t="n">
-        <v>1243</v>
+        <v>874</v>
       </c>
       <c r="H15" t="n">
-        <v>46.81</v>
+        <v>15.65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>269500</v>
+        <v>153500</v>
       </c>
       <c r="K15" t="n">
-        <v>269000</v>
+        <v>155500</v>
       </c>
       <c r="L15" t="n">
-        <v>270500</v>
+        <v>164700</v>
       </c>
       <c r="M15" t="n">
-        <v>263500</v>
+        <v>150700</v>
       </c>
       <c r="N15" t="n">
-        <v>46.85</v>
+        <v>15.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1744771683750</v>
+        <v>314606826750</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>164700</v>
       </c>
       <c r="Q15" t="n">
-        <v>71600</v>
+        <v>87700</v>
       </c>
       <c r="R15" t="n">
-        <v>376000</v>
+        <v>104000</v>
       </c>
       <c r="S15" t="n">
-        <v>-400000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성전자 주가 부진에 대한 부정적 전망. 자사주 매입 및 매크로 변수 불확실성 존재.</t>
+          <t>유가 폭등에 따른 기대감과 단기 급등 후 차익 실현 가능성 언급. 해외 유가 흐름 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['삼성전자', '주가 부진', '자사주']</t>
+          <t>['유가 폭등', '차익 실현', '해외 유가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>151000</v>
+        <v>266500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>336</v>
+        <v>786</v>
       </c>
       <c r="F16" t="n">
-        <v>159</v>
+        <v>467</v>
       </c>
       <c r="G16" t="n">
-        <v>855</v>
+        <v>1223</v>
       </c>
       <c r="H16" t="n">
-        <v>15.65</v>
+        <v>46.81</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>153500</v>
+        <v>269500</v>
       </c>
       <c r="K16" t="n">
-        <v>155500</v>
+        <v>269000</v>
       </c>
       <c r="L16" t="n">
-        <v>164700</v>
+        <v>270500</v>
       </c>
       <c r="M16" t="n">
-        <v>150700</v>
+        <v>263500</v>
       </c>
       <c r="N16" t="n">
-        <v>15.25</v>
+        <v>46.85</v>
       </c>
       <c r="O16" t="n">
-        <v>310525197050</v>
+        <v>1828961500750</v>
       </c>
       <c r="P16" t="n">
-        <v>164700</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>87700</v>
+        <v>71600</v>
       </c>
       <c r="R16" t="n">
-        <v>104000</v>
+        <v>376000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 급등 수혜 기대감과 함께 주가 하락 및 변동성 확대. 단기 차익 실현 및 홀딩 전략 분분.</t>
+          <t>자사주 매입 관련 리스크 언급 및 정치적 이슈와 연계된 부정적 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['SK이노베이션', '유가', '주가 하락']</t>
+          <t>['자사주', '리스크', '정치']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19020</v>
+        <v>19100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>66042079230</v>
+        <v>68574092400</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 투자 관련 기대감과 함께 중동 지정학적 리스크 속 주가 변동성 확대. 대차 거래 내역 주목.</t>
+          <t>미국 투자 및 중동 전쟁 관련 악재 부재 속 급등 기대감 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대우건설', '미국 투자', '지정학적 리스크']</t>
+          <t>['미국 투자', '악재 부재', '급등 기대']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>89200</v>
+        <v>88900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.73%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F18" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G18" t="n">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2082,7 +2082,7 @@
         <v>23.61</v>
       </c>
       <c r="O18" t="n">
-        <v>124153359950</v>
+        <v>128042264400</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2127,83 +2127,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14440</v>
+        <v>6630</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.48%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.34</v>
+        <v>-1.03</v>
       </c>
       <c r="E19" t="n">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
-        <v>406</v>
+        <v>264</v>
       </c>
       <c r="H19" t="n">
-        <v>2.89</v>
+        <v>15.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14960</v>
+        <v>6860</v>
       </c>
       <c r="K19" t="n">
-        <v>15040</v>
+        <v>6800</v>
       </c>
       <c r="L19" t="n">
-        <v>15040</v>
+        <v>6820</v>
       </c>
       <c r="M19" t="n">
-        <v>14190</v>
+        <v>6400</v>
       </c>
       <c r="N19" t="n">
-        <v>1.55</v>
+        <v>16.71</v>
       </c>
       <c r="O19" t="n">
-        <v>74184411575</v>
+        <v>10244328300</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>13000</v>
       </c>
       <c r="Q19" t="n">
-        <v>1263</v>
+        <v>6030</v>
       </c>
       <c r="R19" t="n">
-        <v>-492000</v>
+        <v>-273000</v>
       </c>
       <c r="S19" t="n">
-        <v>-7000</v>
+        <v>-10000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세 속 국내 동반 상승 기대. 외인 매수세 변화 관찰.</t>
+          <t>주가 조작 및 잡주 논란, 외국인 매도세 지속. 분사 및 자사주 소각 등 구조 개선 요구.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외국인']</t>
+          <t>['주가 조작', '외국인 매도', '구조 개선']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6600</v>
+        <v>14420</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.03</v>
+        <v>1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
-        <v>256</v>
+        <v>414</v>
       </c>
       <c r="H20" t="n">
-        <v>15.68</v>
+        <v>2.89</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6860</v>
+        <v>14960</v>
       </c>
       <c r="K20" t="n">
-        <v>6800</v>
+        <v>15040</v>
       </c>
       <c r="L20" t="n">
-        <v>6820</v>
+        <v>15040</v>
       </c>
       <c r="M20" t="n">
-        <v>6400</v>
+        <v>14190</v>
       </c>
       <c r="N20" t="n">
-        <v>16.71</v>
+        <v>1.55</v>
       </c>
       <c r="O20" t="n">
-        <v>10010240150</v>
+        <v>74895854125</v>
       </c>
       <c r="P20" t="n">
-        <v>13000</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>6030</v>
+        <v>1263</v>
       </c>
       <c r="R20" t="n">
-        <v>-273000</v>
+        <v>-492000</v>
       </c>
       <c r="S20" t="n">
-        <v>-10000</v>
+        <v>-7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>자사주 소각 기대감 대비 외인 매도세 및 부정적 의견. 주가 조작 및 잡주 인식.</t>
+          <t>미국 광통신/반도체 강세 및 외국인 순매수 전환 가능성 언급, 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['자사주', '외인', '주가조작']</t>
+          <t>['광통신', '반도체', '외국인 순매수']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15000</v>
+        <v>14990</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.09%</t>
+          <t>-4.16%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F21" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G21" t="n">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>20607590705</v>
+        <v>21023459055</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2421,10 +2421,10 @@
         <v>83</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H22" t="n">
         <v>4.91</v>
@@ -2450,7 +2450,7 @@
         <v>5.26</v>
       </c>
       <c r="O22" t="n">
-        <v>5767823432</v>
+        <v>5801716507</v>
       </c>
       <c r="P22" t="n">
         <v>2705</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3660</v>
+        <v>3670</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.30%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.54</v>
       </c>
       <c r="E23" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H23" t="n">
         <v>1.54</v>
@@ -2542,7 +2542,7 @@
         <v>2.08</v>
       </c>
       <c r="O23" t="n">
-        <v>44536104332</v>
+        <v>44949570574</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>
@@ -2587,70 +2587,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12320</v>
+        <v>29400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-5.47%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.22</v>
+        <v>0.17</v>
       </c>
       <c r="E24" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="H24" t="n">
-        <v>0.14</v>
+        <v>12.31</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>13030</v>
+        <v>31100</v>
       </c>
       <c r="K24" t="n">
-        <v>13160</v>
+        <v>30450</v>
       </c>
       <c r="L24" t="n">
-        <v>13240</v>
+        <v>30600</v>
       </c>
       <c r="M24" t="n">
-        <v>12150</v>
+        <v>28800</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>12.14</v>
       </c>
       <c r="O24" t="n">
-        <v>56166855075</v>
+        <v>49292451975</v>
       </c>
       <c r="P24" t="n">
-        <v>20850</v>
+        <v>75900</v>
       </c>
       <c r="Q24" t="n">
-        <v>4020</v>
+        <v>15000</v>
       </c>
       <c r="R24" t="n">
-        <v>25000</v>
+        <v>-343000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['호재', '원전', '하락']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,99 +2672,99 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29400</v>
+        <v>12160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-5.47%</t>
+          <t>-6.68%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.17</v>
+        <v>-0.22</v>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G25" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="H25" t="n">
-        <v>12.31</v>
+        <v>0.14</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>31100</v>
+        <v>13030</v>
       </c>
       <c r="K25" t="n">
-        <v>30450</v>
+        <v>13160</v>
       </c>
       <c r="L25" t="n">
-        <v>30600</v>
+        <v>13240</v>
       </c>
       <c r="M25" t="n">
-        <v>28800</v>
+        <v>12010</v>
       </c>
       <c r="N25" t="n">
-        <v>12.14</v>
+        <v>0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>47987528675</v>
+        <v>59003785670</v>
       </c>
       <c r="P25" t="n">
-        <v>75900</v>
+        <v>20850</v>
       </c>
       <c r="Q25" t="n">
-        <v>15000</v>
+        <v>4020</v>
       </c>
       <c r="R25" t="n">
-        <v>-343000</v>
+        <v>25000</v>
       </c>
       <c r="S25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>최대 호재 및 그래핀 신소재 관련 기대감, 소규모 매집 정황 감지. 단, 변동성 큰 투자 심리 혼재.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['그래핀', '매집', '신소재']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28200</v>
+        <v>28100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.93%</t>
+          <t>-7.26%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.02</v>
       </c>
       <c r="E26" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F26" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G26" t="n">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>107924506550</v>
+        <v>112043333850</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>의료기기 신규 상장주, 호재에도 불구하고 계단식 하락 및 매도 압력.</t>
+          <t>야간 혈압 관련 호재에도 불구하고 계단식 하락 및 프로그램 매매 흔적. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['신규상장', '의료기기', '계단식하락']</t>
+          <t>['야간 혈압', '계단식 하락', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>-0.32</v>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>
